--- a/datos/Equivalencias_LLYA.xlsx
+++ b/datos/Equivalencias_LLYA.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consumo_horas_educacion_secundaria\datos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5B6277-125C-4260-A888-30B669BFB6BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Equivalencias_LLYA" sheetId="1" r:id="rId4"/>
+    <sheet name="Equivalencias_LLYA" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Equivalencias_LLYA!$A$1:$L$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equivalencias_LLYA!$A$1:$L$66</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -286,23 +296,33 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -310,51 +330,59 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -544,25 +572,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:L1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.5"/>
-    <col customWidth="1" min="2" max="2" width="19.88"/>
-    <col customWidth="1" min="3" max="3" width="12.13"/>
-    <col customWidth="1" min="4" max="5" width="22.63"/>
-    <col customWidth="1" min="6" max="6" width="15.0"/>
-    <col customWidth="1" min="7" max="13" width="22.63"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="5" width="22.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="13" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,7 +631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -608,13 +639,13 @@
         <v>13</v>
       </c>
       <c r="C2" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="5">
-        <v>1671.0</v>
+        <v>1671</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>15</v>
@@ -626,19 +657,19 @@
         <v>17</v>
       </c>
       <c r="I2" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="K2" s="5">
-        <v>3182.0</v>
+        <v>3182</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -646,13 +677,13 @@
         <v>13</v>
       </c>
       <c r="C3" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="5">
-        <v>2778.0</v>
+        <v>2778</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>15</v>
@@ -664,19 +695,19 @@
         <v>17</v>
       </c>
       <c r="I3" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K3" s="5">
-        <v>3193.0</v>
+        <v>3193</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -684,37 +715,37 @@
         <v>13</v>
       </c>
       <c r="C4" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="5">
-        <v>5109.0</v>
+        <v>5109</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I4" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="5">
-        <v>3187.0</v>
+      <c r="K4" s="7">
+        <v>5557</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
@@ -722,13 +753,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="5">
-        <v>1366.0</v>
+        <v>1366</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>15</v>
@@ -740,19 +771,19 @@
         <v>17</v>
       </c>
       <c r="I5" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K5" s="5">
-        <v>3199.0</v>
+        <v>3199</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -760,13 +791,13 @@
         <v>13</v>
       </c>
       <c r="C6" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="5">
-        <v>9166.0</v>
+        <v>9166</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>15</v>
@@ -778,19 +809,19 @@
         <v>17</v>
       </c>
       <c r="I6" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K6" s="5">
-        <v>3186.0</v>
+        <v>3186</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -798,13 +829,13 @@
         <v>13</v>
       </c>
       <c r="C7" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="5">
-        <v>1033.0</v>
+        <v>1033</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>15</v>
@@ -812,7 +843,7 @@
       <c r="I7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -820,13 +851,13 @@
         <v>13</v>
       </c>
       <c r="C8" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="5">
-        <v>5881.0</v>
+        <v>5881</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>15</v>
@@ -838,19 +869,19 @@
         <v>17</v>
       </c>
       <c r="I8" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="5">
-        <v>3185.0</v>
+        <v>3185</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
@@ -858,13 +889,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="5">
-        <v>2533.0</v>
+        <v>2533</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>15</v>
@@ -876,19 +907,19 @@
         <v>17</v>
       </c>
       <c r="I9" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K9" s="5">
-        <v>3189.0</v>
+        <v>3189</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
@@ -896,13 +927,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="5">
-        <v>9584.0</v>
+        <v>9584</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>26</v>
@@ -914,19 +945,19 @@
         <v>17</v>
       </c>
       <c r="I10" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K10" s="5">
-        <v>3192.0</v>
+        <v>3192</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -934,13 +965,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="5">
-        <v>6701.0</v>
+        <v>6701</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>15</v>
@@ -948,7 +979,7 @@
       <c r="I11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
@@ -956,13 +987,13 @@
         <v>13</v>
       </c>
       <c r="C12" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="5">
-        <v>5476.0</v>
+        <v>5476</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>15</v>
@@ -970,7 +1001,7 @@
       <c r="I12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
@@ -978,13 +1009,13 @@
         <v>13</v>
       </c>
       <c r="C13" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="5">
-        <v>7720.0</v>
+        <v>7720</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>26</v>
@@ -996,19 +1027,19 @@
         <v>17</v>
       </c>
       <c r="I13" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K13" s="5">
-        <v>3191.0</v>
+        <v>3191</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
@@ -1016,13 +1047,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="5">
-        <v>7187.0</v>
+        <v>7187</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>15</v>
@@ -1034,19 +1065,19 @@
         <v>32</v>
       </c>
       <c r="I14" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="K14" s="6">
-        <v>2381.0</v>
+        <v>2381</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
@@ -1054,13 +1085,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E15" s="5">
-        <v>1909.0</v>
+        <v>1909</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>15</v>
@@ -1072,19 +1103,19 @@
         <v>32</v>
       </c>
       <c r="I15" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K15" s="6">
-        <v>5469.0</v>
+        <v>5469</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
@@ -1092,13 +1123,13 @@
         <v>13</v>
       </c>
       <c r="C16" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="5">
-        <v>2003.0</v>
+        <v>2003</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>26</v>
@@ -1106,7 +1137,7 @@
       <c r="I16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -1114,13 +1145,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="5">
-        <v>9842.0</v>
+        <v>9842</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>15</v>
@@ -1128,7 +1159,7 @@
       <c r="I17" s="6"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
@@ -1136,13 +1167,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>36</v>
       </c>
       <c r="E18" s="5">
-        <v>5431.0</v>
+        <v>5431</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>15</v>
@@ -1150,7 +1181,7 @@
       <c r="I18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
@@ -1158,13 +1189,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>37</v>
       </c>
       <c r="E19" s="5">
-        <v>5448.0</v>
+        <v>5448</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>15</v>
@@ -1176,19 +1207,19 @@
         <v>17</v>
       </c>
       <c r="I19" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>37</v>
       </c>
       <c r="K19" s="5">
-        <v>3196.0</v>
+        <v>3196</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
@@ -1196,13 +1227,13 @@
         <v>13</v>
       </c>
       <c r="C20" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E20" s="5">
-        <v>4490.0</v>
+        <v>4490</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>26</v>
@@ -1214,19 +1245,19 @@
         <v>17</v>
       </c>
       <c r="I20" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>38</v>
       </c>
       <c r="K20" s="5">
-        <v>3198.0</v>
+        <v>3198</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
@@ -1234,13 +1265,13 @@
         <v>13</v>
       </c>
       <c r="C21" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E21" s="5">
-        <v>8330.0</v>
+        <v>8330</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>26</v>
@@ -1252,19 +1283,19 @@
         <v>17</v>
       </c>
       <c r="I21" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K21" s="5">
-        <v>3184.0</v>
+        <v>3184</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>12</v>
       </c>
@@ -1272,13 +1303,13 @@
         <v>13</v>
       </c>
       <c r="C22" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E22" s="5">
-        <v>3252.0</v>
+        <v>3252</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>15</v>
@@ -1286,7 +1317,7 @@
       <c r="I22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>12</v>
       </c>
@@ -1294,13 +1325,13 @@
         <v>13</v>
       </c>
       <c r="C23" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E23" s="5">
-        <v>4432.0</v>
+        <v>4432</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>26</v>
@@ -1308,7 +1339,7 @@
       <c r="I23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>12</v>
       </c>
@@ -1316,13 +1347,13 @@
         <v>13</v>
       </c>
       <c r="C24" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E24" s="5">
-        <v>4661.0</v>
+        <v>4661</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>15</v>
@@ -1330,7 +1361,7 @@
       <c r="I24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>12</v>
       </c>
@@ -1338,13 +1369,13 @@
         <v>13</v>
       </c>
       <c r="C25" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="5">
-        <v>3064.0</v>
+        <v>3064</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>15</v>
@@ -1356,19 +1387,19 @@
         <v>17</v>
       </c>
       <c r="I25" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>43</v>
       </c>
       <c r="K25" s="5">
-        <v>3215.0</v>
+        <v>3215</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -1376,13 +1407,13 @@
         <v>13</v>
       </c>
       <c r="C26" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E26" s="5">
-        <v>2434.0</v>
+        <v>2434</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>15</v>
@@ -1394,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="I26" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K26" s="5">
-        <v>3203.0</v>
+        <v>3203</v>
       </c>
       <c r="L26" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>12</v>
       </c>
@@ -1414,13 +1445,13 @@
         <v>13</v>
       </c>
       <c r="C27" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="5">
-        <v>8726.0</v>
+        <v>8726</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>15</v>
@@ -1428,7 +1459,7 @@
       <c r="I27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>12</v>
       </c>
@@ -1436,13 +1467,13 @@
         <v>13</v>
       </c>
       <c r="C28" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E28" s="5">
-        <v>8518.0</v>
+        <v>8518</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>15</v>
@@ -1454,19 +1485,19 @@
         <v>17</v>
       </c>
       <c r="I28" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>46</v>
       </c>
       <c r="K28" s="5">
-        <v>3195.0</v>
+        <v>3195</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>12</v>
       </c>
@@ -1474,13 +1505,13 @@
         <v>13</v>
       </c>
       <c r="C29" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E29" s="5">
-        <v>8717.0</v>
+        <v>8717</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>15</v>
@@ -1488,7 +1519,7 @@
       <c r="I29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>12</v>
       </c>
@@ -1496,13 +1527,13 @@
         <v>13</v>
       </c>
       <c r="C30" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E30" s="5">
-        <v>4604.0</v>
+        <v>4604</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>15</v>
@@ -1514,19 +1545,19 @@
         <v>17</v>
       </c>
       <c r="I30" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>48</v>
       </c>
       <c r="K30" s="5">
-        <v>3210.0</v>
+        <v>3210</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>12</v>
       </c>
@@ -1534,13 +1565,13 @@
         <v>13</v>
       </c>
       <c r="C31" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="5">
-        <v>8588.0</v>
+        <v>8588</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>15</v>
@@ -1552,19 +1583,19 @@
         <v>17</v>
       </c>
       <c r="I31" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>49</v>
       </c>
       <c r="K31" s="5">
-        <v>3209.0</v>
+        <v>3209</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>12</v>
       </c>
@@ -1572,13 +1603,13 @@
         <v>13</v>
       </c>
       <c r="C32" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E32" s="5">
-        <v>3079.0</v>
+        <v>3079</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>26</v>
@@ -1590,19 +1621,19 @@
         <v>17</v>
       </c>
       <c r="I32" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>50</v>
       </c>
       <c r="K32" s="5">
-        <v>3202.0</v>
+        <v>3202</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>12</v>
       </c>
@@ -1610,13 +1641,13 @@
         <v>13</v>
       </c>
       <c r="C33" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>51</v>
       </c>
       <c r="E33" s="5">
-        <v>1512.0</v>
+        <v>1512</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>15</v>
@@ -1628,19 +1659,19 @@
         <v>17</v>
       </c>
       <c r="I33" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>51</v>
       </c>
       <c r="K33" s="5">
-        <v>3197.0</v>
+        <v>3197</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>12</v>
       </c>
@@ -1648,13 +1679,13 @@
         <v>13</v>
       </c>
       <c r="C34" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>52</v>
       </c>
       <c r="E34" s="5">
-        <v>1793.0</v>
+        <v>1793</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>15</v>
@@ -1666,19 +1697,19 @@
         <v>17</v>
       </c>
       <c r="I34" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>52</v>
       </c>
       <c r="K34" s="5">
-        <v>3190.0</v>
+        <v>3190</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>12</v>
       </c>
@@ -1686,13 +1717,13 @@
         <v>13</v>
       </c>
       <c r="C35" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E35" s="5">
-        <v>4202.0</v>
+        <v>4202</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>15</v>
@@ -1704,19 +1735,19 @@
         <v>17</v>
       </c>
       <c r="I35" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>53</v>
       </c>
       <c r="K35" s="5">
-        <v>3214.0</v>
+        <v>3214</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>12</v>
       </c>
@@ -1724,13 +1755,13 @@
         <v>13</v>
       </c>
       <c r="C36" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E36" s="5">
-        <v>2063.0</v>
+        <v>2063</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>15</v>
@@ -1738,7 +1769,7 @@
       <c r="I36" s="6"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>12</v>
       </c>
@@ -1746,13 +1777,13 @@
         <v>13</v>
       </c>
       <c r="C37" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E37" s="5">
-        <v>5423.0</v>
+        <v>5423</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>26</v>
@@ -1764,19 +1795,19 @@
         <v>17</v>
       </c>
       <c r="I37" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>55</v>
       </c>
       <c r="K37" s="5">
-        <v>3590.0</v>
+        <v>3590</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>12</v>
       </c>
@@ -1784,13 +1815,13 @@
         <v>13</v>
       </c>
       <c r="C38" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>56</v>
       </c>
       <c r="E38" s="5">
-        <v>7045.0</v>
+        <v>7045</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>15</v>
@@ -1798,7 +1829,7 @@
       <c r="I38" s="6"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>12</v>
       </c>
@@ -1806,13 +1837,13 @@
         <v>13</v>
       </c>
       <c r="C39" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E39" s="5">
-        <v>4629.0</v>
+        <v>4629</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>15</v>
@@ -1820,7 +1851,7 @@
       <c r="I39" s="6"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>12</v>
       </c>
@@ -1828,13 +1859,13 @@
         <v>13</v>
       </c>
       <c r="C40" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>58</v>
       </c>
       <c r="E40" s="5">
-        <v>7113.0</v>
+        <v>7113</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>15</v>
@@ -1842,7 +1873,7 @@
       <c r="I40" s="6"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>12</v>
       </c>
@@ -1850,13 +1881,13 @@
         <v>13</v>
       </c>
       <c r="C41" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>59</v>
       </c>
       <c r="E41" s="5">
-        <v>8636.0</v>
+        <v>8636</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>15</v>
@@ -1868,19 +1899,19 @@
         <v>32</v>
       </c>
       <c r="I41" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>59</v>
       </c>
       <c r="K41" s="6">
-        <v>8636.0</v>
+        <v>8636</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>12</v>
       </c>
@@ -1888,13 +1919,13 @@
         <v>13</v>
       </c>
       <c r="C42" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>60</v>
       </c>
       <c r="E42" s="5">
-        <v>6776.0</v>
+        <v>6776</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>15</v>
@@ -1906,19 +1937,19 @@
         <v>17</v>
       </c>
       <c r="I42" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>61</v>
       </c>
       <c r="K42" s="5">
-        <v>3228.0</v>
+        <v>3228</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>12</v>
       </c>
@@ -1926,13 +1957,13 @@
         <v>13</v>
       </c>
       <c r="C43" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>62</v>
       </c>
       <c r="E43" s="5">
-        <v>7627.0</v>
+        <v>7627</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>15</v>
@@ -1940,7 +1971,7 @@
       <c r="I43" s="6"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>12</v>
       </c>
@@ -1948,13 +1979,13 @@
         <v>13</v>
       </c>
       <c r="C44" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E44" s="5">
-        <v>1822.0</v>
+        <v>1822</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>15</v>
@@ -1966,19 +1997,19 @@
         <v>17</v>
       </c>
       <c r="I44" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>63</v>
       </c>
       <c r="K44" s="5">
-        <v>3226.0</v>
+        <v>3226</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>12</v>
       </c>
@@ -1986,13 +2017,13 @@
         <v>13</v>
       </c>
       <c r="C45" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>64</v>
       </c>
       <c r="E45" s="5">
-        <v>7794.0</v>
+        <v>7794</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>15</v>
@@ -2004,19 +2035,19 @@
         <v>66</v>
       </c>
       <c r="I45" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>64</v>
       </c>
       <c r="K45" s="5">
-        <v>3598.0</v>
+        <v>3598</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>12</v>
       </c>
@@ -2024,13 +2055,13 @@
         <v>13</v>
       </c>
       <c r="C46" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>67</v>
       </c>
       <c r="E46" s="5">
-        <v>9734.0</v>
+        <v>9734</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>15</v>
@@ -2038,7 +2069,7 @@
       <c r="I46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>12</v>
       </c>
@@ -2046,13 +2077,13 @@
         <v>13</v>
       </c>
       <c r="C47" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>68</v>
       </c>
       <c r="E47" s="5">
-        <v>5080.0</v>
+        <v>5080</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>15</v>
@@ -2060,7 +2091,7 @@
       <c r="I47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>12</v>
       </c>
@@ -2068,13 +2099,13 @@
         <v>13</v>
       </c>
       <c r="C48" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E48" s="5">
-        <v>3762.0</v>
+        <v>3762</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>15</v>
@@ -2086,19 +2117,19 @@
         <v>17</v>
       </c>
       <c r="I48" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>69</v>
       </c>
       <c r="K48" s="5">
-        <v>3205.0</v>
+        <v>3205</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>12</v>
       </c>
@@ -2106,13 +2137,13 @@
         <v>13</v>
       </c>
       <c r="C49" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E49" s="5">
-        <v>9807.0</v>
+        <v>9807</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>15</v>
@@ -2124,19 +2155,19 @@
         <v>17</v>
       </c>
       <c r="I49" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>61</v>
       </c>
       <c r="K49" s="5">
-        <v>3228.0</v>
+        <v>3228</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>12</v>
       </c>
@@ -2144,13 +2175,13 @@
         <v>13</v>
       </c>
       <c r="C50" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>70</v>
       </c>
       <c r="E50" s="5">
-        <v>7773.0</v>
+        <v>7773</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>15</v>
@@ -2162,19 +2193,19 @@
         <v>17</v>
       </c>
       <c r="I50" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K50" s="5">
-        <v>3246.0</v>
+        <v>3246</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>12</v>
       </c>
@@ -2182,13 +2213,13 @@
         <v>13</v>
       </c>
       <c r="C51" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>71</v>
       </c>
       <c r="E51" s="5">
-        <v>1240.0</v>
+        <v>1240</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>15</v>
@@ -2200,19 +2231,19 @@
         <v>17</v>
       </c>
       <c r="I51" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>71</v>
       </c>
       <c r="K51" s="5">
-        <v>3247.0</v>
+        <v>3247</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>12</v>
       </c>
@@ -2220,13 +2251,13 @@
         <v>13</v>
       </c>
       <c r="C52" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>72</v>
       </c>
       <c r="E52" s="5">
-        <v>2632.0</v>
+        <v>2632</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>26</v>
@@ -2238,19 +2269,19 @@
         <v>17</v>
       </c>
       <c r="I52" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>72</v>
       </c>
       <c r="K52" s="5">
-        <v>3252.0</v>
+        <v>3252</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>12</v>
       </c>
@@ -2258,13 +2289,13 @@
         <v>13</v>
       </c>
       <c r="C53" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>73</v>
       </c>
       <c r="E53" s="5">
-        <v>6434.0</v>
+        <v>6434</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>15</v>
@@ -2272,7 +2303,7 @@
       <c r="I53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>12</v>
       </c>
@@ -2280,13 +2311,13 @@
         <v>13</v>
       </c>
       <c r="C54" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>74</v>
       </c>
       <c r="E54" s="5">
-        <v>1804.0</v>
+        <v>1804</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>15</v>
@@ -2294,7 +2325,7 @@
       <c r="I54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>12</v>
       </c>
@@ -2302,13 +2333,13 @@
         <v>13</v>
       </c>
       <c r="C55" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>75</v>
       </c>
       <c r="E55" s="5">
-        <v>9935.0</v>
+        <v>9935</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>15</v>
@@ -2320,19 +2351,19 @@
         <v>32</v>
       </c>
       <c r="I55" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>75</v>
       </c>
       <c r="K55" s="6">
-        <v>2283.0</v>
+        <v>2283</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>12</v>
       </c>
@@ -2340,13 +2371,13 @@
         <v>13</v>
       </c>
       <c r="C56" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E56" s="5">
-        <v>5166.0</v>
+        <v>5166</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>26</v>
@@ -2358,7 +2389,7 @@
         <v>17</v>
       </c>
       <c r="I56" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>77</v>
@@ -2370,7 +2401,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>12</v>
       </c>
@@ -2378,13 +2409,13 @@
         <v>13</v>
       </c>
       <c r="C57" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>79</v>
       </c>
       <c r="E57" s="5">
-        <v>6050.0</v>
+        <v>6050</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>15</v>
@@ -2396,19 +2427,19 @@
         <v>32</v>
       </c>
       <c r="I57" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>79</v>
       </c>
       <c r="K57" s="6">
-        <v>1433.0</v>
+        <v>1433</v>
       </c>
       <c r="L57" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>12</v>
       </c>
@@ -2416,13 +2447,13 @@
         <v>13</v>
       </c>
       <c r="C58" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>80</v>
       </c>
       <c r="E58" s="5">
-        <v>5079.0</v>
+        <v>5079</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>26</v>
@@ -2430,7 +2461,7 @@
       <c r="I58" s="6"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>12</v>
       </c>
@@ -2438,13 +2469,13 @@
         <v>13</v>
       </c>
       <c r="C59" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>81</v>
       </c>
       <c r="E59" s="5">
-        <v>3312.0</v>
+        <v>3312</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>15</v>
@@ -2456,19 +2487,19 @@
         <v>17</v>
       </c>
       <c r="I59" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>81</v>
       </c>
       <c r="K59" s="5">
-        <v>3230.0</v>
+        <v>3230</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>12</v>
       </c>
@@ -2476,13 +2507,13 @@
         <v>13</v>
       </c>
       <c r="C60" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>82</v>
       </c>
       <c r="E60" s="5">
-        <v>1087.0</v>
+        <v>1087</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>26</v>
@@ -2494,19 +2525,19 @@
         <v>17</v>
       </c>
       <c r="I60" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>82</v>
       </c>
       <c r="K60" s="5">
-        <v>3256.0</v>
+        <v>3256</v>
       </c>
       <c r="L60" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>12</v>
       </c>
@@ -2514,13 +2545,13 @@
         <v>13</v>
       </c>
       <c r="C61" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>83</v>
       </c>
       <c r="E61" s="5">
-        <v>3332.0</v>
+        <v>3332</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>15</v>
@@ -2528,7 +2559,7 @@
       <c r="I61" s="6"/>
       <c r="K61" s="6"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>12</v>
       </c>
@@ -2536,13 +2567,13 @@
         <v>13</v>
       </c>
       <c r="C62" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E62" s="5">
-        <v>1490.0</v>
+        <v>1490</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>15</v>
@@ -2554,19 +2585,19 @@
         <v>17</v>
       </c>
       <c r="I62" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>84</v>
       </c>
       <c r="K62" s="5">
-        <v>3218.0</v>
+        <v>3218</v>
       </c>
       <c r="L62" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>12</v>
       </c>
@@ -2574,13 +2605,13 @@
         <v>13</v>
       </c>
       <c r="C63" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>85</v>
       </c>
       <c r="E63" s="5">
-        <v>6053.0</v>
+        <v>6053</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>26</v>
@@ -2592,19 +2623,19 @@
         <v>32</v>
       </c>
       <c r="I63" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>85</v>
       </c>
       <c r="K63" s="6">
-        <v>1127.0</v>
+        <v>1127</v>
       </c>
       <c r="L63" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>12</v>
       </c>
@@ -2612,13 +2643,13 @@
         <v>13</v>
       </c>
       <c r="C64" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>86</v>
       </c>
       <c r="E64" s="5">
-        <v>9845.0</v>
+        <v>9845</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>15</v>
@@ -2630,19 +2661,19 @@
         <v>17</v>
       </c>
       <c r="I64" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>86</v>
       </c>
       <c r="K64" s="5">
-        <v>3253.0</v>
+        <v>3253</v>
       </c>
       <c r="L64" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>12</v>
       </c>
@@ -2650,13 +2681,13 @@
         <v>13</v>
       </c>
       <c r="C65" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>87</v>
       </c>
       <c r="E65" s="5">
-        <v>8373.0</v>
+        <v>8373</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>26</v>
@@ -2668,19 +2699,19 @@
         <v>17</v>
       </c>
       <c r="I65" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>87</v>
       </c>
       <c r="K65" s="5">
-        <v>3263.0</v>
+        <v>3263</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>12</v>
       </c>
@@ -2688,13 +2719,13 @@
         <v>13</v>
       </c>
       <c r="C66" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>88</v>
       </c>
       <c r="E66" s="5">
-        <v>3242.0</v>
+        <v>3242</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>15</v>
@@ -2702,5612 +2733,5612 @@
       <c r="I66" s="6"/>
       <c r="K66" s="6"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C67" s="6"/>
       <c r="F67" s="6"/>
       <c r="I67" s="6"/>
       <c r="K67" s="6"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C68" s="6"/>
       <c r="F68" s="6"/>
       <c r="I68" s="6"/>
       <c r="K68" s="6"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C69" s="6"/>
       <c r="F69" s="6"/>
       <c r="I69" s="6"/>
       <c r="K69" s="6"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C70" s="6"/>
       <c r="F70" s="6"/>
       <c r="I70" s="6"/>
       <c r="K70" s="6"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C71" s="6"/>
       <c r="F71" s="6"/>
       <c r="I71" s="6"/>
       <c r="K71" s="6"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C72" s="6"/>
       <c r="F72" s="6"/>
       <c r="I72" s="6"/>
       <c r="K72" s="6"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C73" s="6"/>
       <c r="F73" s="6"/>
       <c r="I73" s="6"/>
       <c r="K73" s="6"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C74" s="6"/>
       <c r="F74" s="6"/>
       <c r="I74" s="6"/>
       <c r="K74" s="6"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C75" s="6"/>
       <c r="F75" s="6"/>
       <c r="I75" s="6"/>
       <c r="K75" s="6"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C76" s="6"/>
       <c r="F76" s="6"/>
       <c r="I76" s="6"/>
       <c r="K76" s="6"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C77" s="6"/>
       <c r="F77" s="6"/>
       <c r="I77" s="6"/>
       <c r="K77" s="6"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C78" s="6"/>
       <c r="F78" s="6"/>
       <c r="I78" s="6"/>
       <c r="K78" s="6"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C79" s="6"/>
       <c r="F79" s="6"/>
       <c r="I79" s="6"/>
       <c r="K79" s="6"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C80" s="6"/>
       <c r="F80" s="6"/>
       <c r="I80" s="6"/>
       <c r="K80" s="6"/>
     </row>
-    <row r="81">
+    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C81" s="6"/>
       <c r="F81" s="6"/>
       <c r="I81" s="6"/>
       <c r="K81" s="6"/>
     </row>
-    <row r="82">
+    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C82" s="6"/>
       <c r="F82" s="6"/>
       <c r="I82" s="6"/>
       <c r="K82" s="6"/>
     </row>
-    <row r="83">
+    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C83" s="6"/>
       <c r="F83" s="6"/>
       <c r="I83" s="6"/>
       <c r="K83" s="6"/>
     </row>
-    <row r="84">
+    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C84" s="6"/>
       <c r="F84" s="6"/>
       <c r="I84" s="6"/>
       <c r="K84" s="6"/>
     </row>
-    <row r="85">
+    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C85" s="6"/>
       <c r="F85" s="6"/>
       <c r="I85" s="6"/>
       <c r="K85" s="6"/>
     </row>
-    <row r="86">
+    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C86" s="6"/>
       <c r="F86" s="6"/>
       <c r="I86" s="6"/>
       <c r="K86" s="6"/>
     </row>
-    <row r="87">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C87" s="6"/>
       <c r="F87" s="6"/>
       <c r="I87" s="6"/>
       <c r="K87" s="6"/>
     </row>
-    <row r="88">
+    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C88" s="6"/>
       <c r="F88" s="6"/>
       <c r="I88" s="6"/>
       <c r="K88" s="6"/>
     </row>
-    <row r="89">
+    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C89" s="6"/>
       <c r="F89" s="6"/>
       <c r="I89" s="6"/>
       <c r="K89" s="6"/>
     </row>
-    <row r="90">
+    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C90" s="6"/>
       <c r="F90" s="6"/>
       <c r="I90" s="6"/>
       <c r="K90" s="6"/>
     </row>
-    <row r="91">
+    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C91" s="6"/>
       <c r="F91" s="6"/>
       <c r="I91" s="6"/>
       <c r="K91" s="6"/>
     </row>
-    <row r="92">
+    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C92" s="6"/>
       <c r="F92" s="6"/>
       <c r="I92" s="6"/>
       <c r="K92" s="6"/>
     </row>
-    <row r="93">
+    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C93" s="6"/>
       <c r="F93" s="6"/>
       <c r="I93" s="6"/>
       <c r="K93" s="6"/>
     </row>
-    <row r="94">
+    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C94" s="6"/>
       <c r="F94" s="6"/>
       <c r="I94" s="6"/>
       <c r="K94" s="6"/>
     </row>
-    <row r="95">
+    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C95" s="6"/>
       <c r="F95" s="6"/>
       <c r="I95" s="6"/>
       <c r="K95" s="6"/>
     </row>
-    <row r="96">
+    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C96" s="6"/>
       <c r="F96" s="6"/>
       <c r="I96" s="6"/>
       <c r="K96" s="6"/>
     </row>
-    <row r="97">
+    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C97" s="6"/>
       <c r="F97" s="6"/>
       <c r="I97" s="6"/>
       <c r="K97" s="6"/>
     </row>
-    <row r="98">
+    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C98" s="6"/>
       <c r="F98" s="6"/>
       <c r="I98" s="6"/>
       <c r="K98" s="6"/>
     </row>
-    <row r="99">
+    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C99" s="6"/>
       <c r="F99" s="6"/>
       <c r="I99" s="6"/>
       <c r="K99" s="6"/>
     </row>
-    <row r="100">
+    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C100" s="6"/>
       <c r="F100" s="6"/>
       <c r="I100" s="6"/>
       <c r="K100" s="6"/>
     </row>
-    <row r="101">
+    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C101" s="6"/>
       <c r="F101" s="6"/>
       <c r="I101" s="6"/>
       <c r="K101" s="6"/>
     </row>
-    <row r="102">
+    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C102" s="6"/>
       <c r="F102" s="6"/>
       <c r="I102" s="6"/>
       <c r="K102" s="6"/>
     </row>
-    <row r="103">
+    <row r="103" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C103" s="6"/>
       <c r="F103" s="6"/>
       <c r="I103" s="6"/>
       <c r="K103" s="6"/>
     </row>
-    <row r="104">
+    <row r="104" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C104" s="6"/>
       <c r="F104" s="6"/>
       <c r="I104" s="6"/>
       <c r="K104" s="6"/>
     </row>
-    <row r="105">
+    <row r="105" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C105" s="6"/>
       <c r="F105" s="6"/>
       <c r="I105" s="6"/>
       <c r="K105" s="6"/>
     </row>
-    <row r="106">
+    <row r="106" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C106" s="6"/>
       <c r="F106" s="6"/>
       <c r="I106" s="6"/>
       <c r="K106" s="6"/>
     </row>
-    <row r="107">
+    <row r="107" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C107" s="6"/>
       <c r="F107" s="6"/>
       <c r="I107" s="6"/>
       <c r="K107" s="6"/>
     </row>
-    <row r="108">
+    <row r="108" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C108" s="6"/>
       <c r="F108" s="6"/>
       <c r="I108" s="6"/>
       <c r="K108" s="6"/>
     </row>
-    <row r="109">
+    <row r="109" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C109" s="6"/>
       <c r="F109" s="6"/>
       <c r="I109" s="6"/>
       <c r="K109" s="6"/>
     </row>
-    <row r="110">
+    <row r="110" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C110" s="6"/>
       <c r="F110" s="6"/>
       <c r="I110" s="6"/>
       <c r="K110" s="6"/>
     </row>
-    <row r="111">
+    <row r="111" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C111" s="6"/>
       <c r="F111" s="6"/>
       <c r="I111" s="6"/>
       <c r="K111" s="6"/>
     </row>
-    <row r="112">
+    <row r="112" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C112" s="6"/>
       <c r="F112" s="6"/>
       <c r="I112" s="6"/>
       <c r="K112" s="6"/>
     </row>
-    <row r="113">
+    <row r="113" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C113" s="6"/>
       <c r="F113" s="6"/>
       <c r="I113" s="6"/>
       <c r="K113" s="6"/>
     </row>
-    <row r="114">
+    <row r="114" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C114" s="6"/>
       <c r="F114" s="6"/>
       <c r="I114" s="6"/>
       <c r="K114" s="6"/>
     </row>
-    <row r="115">
+    <row r="115" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C115" s="6"/>
       <c r="F115" s="6"/>
       <c r="I115" s="6"/>
       <c r="K115" s="6"/>
     </row>
-    <row r="116">
+    <row r="116" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C116" s="6"/>
       <c r="F116" s="6"/>
       <c r="I116" s="6"/>
       <c r="K116" s="6"/>
     </row>
-    <row r="117">
+    <row r="117" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C117" s="6"/>
       <c r="F117" s="6"/>
       <c r="I117" s="6"/>
       <c r="K117" s="6"/>
     </row>
-    <row r="118">
+    <row r="118" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C118" s="6"/>
       <c r="F118" s="6"/>
       <c r="I118" s="6"/>
       <c r="K118" s="6"/>
     </row>
-    <row r="119">
+    <row r="119" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C119" s="6"/>
       <c r="F119" s="6"/>
       <c r="I119" s="6"/>
       <c r="K119" s="6"/>
     </row>
-    <row r="120">
+    <row r="120" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C120" s="6"/>
       <c r="F120" s="6"/>
       <c r="I120" s="6"/>
       <c r="K120" s="6"/>
     </row>
-    <row r="121">
+    <row r="121" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C121" s="6"/>
       <c r="F121" s="6"/>
       <c r="I121" s="6"/>
       <c r="K121" s="6"/>
     </row>
-    <row r="122">
+    <row r="122" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C122" s="6"/>
       <c r="F122" s="6"/>
       <c r="I122" s="6"/>
       <c r="K122" s="6"/>
     </row>
-    <row r="123">
+    <row r="123" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C123" s="6"/>
       <c r="F123" s="6"/>
       <c r="I123" s="6"/>
       <c r="K123" s="6"/>
     </row>
-    <row r="124">
+    <row r="124" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C124" s="6"/>
       <c r="F124" s="6"/>
       <c r="I124" s="6"/>
       <c r="K124" s="6"/>
     </row>
-    <row r="125">
+    <row r="125" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C125" s="6"/>
       <c r="F125" s="6"/>
       <c r="I125" s="6"/>
       <c r="K125" s="6"/>
     </row>
-    <row r="126">
+    <row r="126" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C126" s="6"/>
       <c r="F126" s="6"/>
       <c r="I126" s="6"/>
       <c r="K126" s="6"/>
     </row>
-    <row r="127">
+    <row r="127" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C127" s="6"/>
       <c r="F127" s="6"/>
       <c r="I127" s="6"/>
       <c r="K127" s="6"/>
     </row>
-    <row r="128">
+    <row r="128" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C128" s="6"/>
       <c r="F128" s="6"/>
       <c r="I128" s="6"/>
       <c r="K128" s="6"/>
     </row>
-    <row r="129">
+    <row r="129" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C129" s="6"/>
       <c r="F129" s="6"/>
       <c r="I129" s="6"/>
       <c r="K129" s="6"/>
     </row>
-    <row r="130">
+    <row r="130" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C130" s="6"/>
       <c r="F130" s="6"/>
       <c r="I130" s="6"/>
       <c r="K130" s="6"/>
     </row>
-    <row r="131">
+    <row r="131" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C131" s="6"/>
       <c r="F131" s="6"/>
       <c r="I131" s="6"/>
       <c r="K131" s="6"/>
     </row>
-    <row r="132">
+    <row r="132" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C132" s="6"/>
       <c r="F132" s="6"/>
       <c r="I132" s="6"/>
       <c r="K132" s="6"/>
     </row>
-    <row r="133">
+    <row r="133" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C133" s="6"/>
       <c r="F133" s="6"/>
       <c r="I133" s="6"/>
       <c r="K133" s="6"/>
     </row>
-    <row r="134">
+    <row r="134" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C134" s="6"/>
       <c r="F134" s="6"/>
       <c r="I134" s="6"/>
       <c r="K134" s="6"/>
     </row>
-    <row r="135">
+    <row r="135" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C135" s="6"/>
       <c r="F135" s="6"/>
       <c r="I135" s="6"/>
       <c r="K135" s="6"/>
     </row>
-    <row r="136">
+    <row r="136" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C136" s="6"/>
       <c r="F136" s="6"/>
       <c r="I136" s="6"/>
       <c r="K136" s="6"/>
     </row>
-    <row r="137">
+    <row r="137" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C137" s="6"/>
       <c r="F137" s="6"/>
       <c r="I137" s="6"/>
       <c r="K137" s="6"/>
     </row>
-    <row r="138">
+    <row r="138" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C138" s="6"/>
       <c r="F138" s="6"/>
       <c r="I138" s="6"/>
       <c r="K138" s="6"/>
     </row>
-    <row r="139">
+    <row r="139" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C139" s="6"/>
       <c r="F139" s="6"/>
       <c r="I139" s="6"/>
       <c r="K139" s="6"/>
     </row>
-    <row r="140">
+    <row r="140" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C140" s="6"/>
       <c r="F140" s="6"/>
       <c r="I140" s="6"/>
       <c r="K140" s="6"/>
     </row>
-    <row r="141">
+    <row r="141" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C141" s="6"/>
       <c r="F141" s="6"/>
       <c r="I141" s="6"/>
       <c r="K141" s="6"/>
     </row>
-    <row r="142">
+    <row r="142" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C142" s="6"/>
       <c r="F142" s="6"/>
       <c r="I142" s="6"/>
       <c r="K142" s="6"/>
     </row>
-    <row r="143">
+    <row r="143" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C143" s="6"/>
       <c r="F143" s="6"/>
       <c r="I143" s="6"/>
       <c r="K143" s="6"/>
     </row>
-    <row r="144">
+    <row r="144" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C144" s="6"/>
       <c r="F144" s="6"/>
       <c r="I144" s="6"/>
       <c r="K144" s="6"/>
     </row>
-    <row r="145">
+    <row r="145" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C145" s="6"/>
       <c r="F145" s="6"/>
       <c r="I145" s="6"/>
       <c r="K145" s="6"/>
     </row>
-    <row r="146">
+    <row r="146" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C146" s="6"/>
       <c r="F146" s="6"/>
       <c r="I146" s="6"/>
       <c r="K146" s="6"/>
     </row>
-    <row r="147">
+    <row r="147" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C147" s="6"/>
       <c r="F147" s="6"/>
       <c r="I147" s="6"/>
       <c r="K147" s="6"/>
     </row>
-    <row r="148">
+    <row r="148" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C148" s="6"/>
       <c r="F148" s="6"/>
       <c r="I148" s="6"/>
       <c r="K148" s="6"/>
     </row>
-    <row r="149">
+    <row r="149" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C149" s="6"/>
       <c r="F149" s="6"/>
       <c r="I149" s="6"/>
       <c r="K149" s="6"/>
     </row>
-    <row r="150">
+    <row r="150" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C150" s="6"/>
       <c r="F150" s="6"/>
       <c r="I150" s="6"/>
       <c r="K150" s="6"/>
     </row>
-    <row r="151">
+    <row r="151" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C151" s="6"/>
       <c r="F151" s="6"/>
       <c r="I151" s="6"/>
       <c r="K151" s="6"/>
     </row>
-    <row r="152">
+    <row r="152" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C152" s="6"/>
       <c r="F152" s="6"/>
       <c r="I152" s="6"/>
       <c r="K152" s="6"/>
     </row>
-    <row r="153">
+    <row r="153" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C153" s="6"/>
       <c r="F153" s="6"/>
       <c r="I153" s="6"/>
       <c r="K153" s="6"/>
     </row>
-    <row r="154">
+    <row r="154" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C154" s="6"/>
       <c r="F154" s="6"/>
       <c r="I154" s="6"/>
       <c r="K154" s="6"/>
     </row>
-    <row r="155">
+    <row r="155" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C155" s="6"/>
       <c r="F155" s="6"/>
       <c r="I155" s="6"/>
       <c r="K155" s="6"/>
     </row>
-    <row r="156">
+    <row r="156" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C156" s="6"/>
       <c r="F156" s="6"/>
       <c r="I156" s="6"/>
       <c r="K156" s="6"/>
     </row>
-    <row r="157">
+    <row r="157" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C157" s="6"/>
       <c r="F157" s="6"/>
       <c r="I157" s="6"/>
       <c r="K157" s="6"/>
     </row>
-    <row r="158">
+    <row r="158" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C158" s="6"/>
       <c r="F158" s="6"/>
       <c r="I158" s="6"/>
       <c r="K158" s="6"/>
     </row>
-    <row r="159">
+    <row r="159" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C159" s="6"/>
       <c r="F159" s="6"/>
       <c r="I159" s="6"/>
       <c r="K159" s="6"/>
     </row>
-    <row r="160">
+    <row r="160" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C160" s="6"/>
       <c r="F160" s="6"/>
       <c r="I160" s="6"/>
       <c r="K160" s="6"/>
     </row>
-    <row r="161">
+    <row r="161" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C161" s="6"/>
       <c r="F161" s="6"/>
       <c r="I161" s="6"/>
       <c r="K161" s="6"/>
     </row>
-    <row r="162">
+    <row r="162" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C162" s="6"/>
       <c r="F162" s="6"/>
       <c r="I162" s="6"/>
       <c r="K162" s="6"/>
     </row>
-    <row r="163">
+    <row r="163" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C163" s="6"/>
       <c r="F163" s="6"/>
       <c r="I163" s="6"/>
       <c r="K163" s="6"/>
     </row>
-    <row r="164">
+    <row r="164" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C164" s="6"/>
       <c r="F164" s="6"/>
       <c r="I164" s="6"/>
       <c r="K164" s="6"/>
     </row>
-    <row r="165">
+    <row r="165" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C165" s="6"/>
       <c r="F165" s="6"/>
       <c r="I165" s="6"/>
       <c r="K165" s="6"/>
     </row>
-    <row r="166">
+    <row r="166" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C166" s="6"/>
       <c r="F166" s="6"/>
       <c r="I166" s="6"/>
       <c r="K166" s="6"/>
     </row>
-    <row r="167">
+    <row r="167" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C167" s="6"/>
       <c r="F167" s="6"/>
       <c r="I167" s="6"/>
       <c r="K167" s="6"/>
     </row>
-    <row r="168">
+    <row r="168" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C168" s="6"/>
       <c r="F168" s="6"/>
       <c r="I168" s="6"/>
       <c r="K168" s="6"/>
     </row>
-    <row r="169">
+    <row r="169" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C169" s="6"/>
       <c r="F169" s="6"/>
       <c r="I169" s="6"/>
       <c r="K169" s="6"/>
     </row>
-    <row r="170">
+    <row r="170" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C170" s="6"/>
       <c r="F170" s="6"/>
       <c r="I170" s="6"/>
       <c r="K170" s="6"/>
     </row>
-    <row r="171">
+    <row r="171" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C171" s="6"/>
       <c r="F171" s="6"/>
       <c r="I171" s="6"/>
       <c r="K171" s="6"/>
     </row>
-    <row r="172">
+    <row r="172" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C172" s="6"/>
       <c r="F172" s="6"/>
       <c r="I172" s="6"/>
       <c r="K172" s="6"/>
     </row>
-    <row r="173">
+    <row r="173" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C173" s="6"/>
       <c r="F173" s="6"/>
       <c r="I173" s="6"/>
       <c r="K173" s="6"/>
     </row>
-    <row r="174">
+    <row r="174" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C174" s="6"/>
       <c r="F174" s="6"/>
       <c r="I174" s="6"/>
       <c r="K174" s="6"/>
     </row>
-    <row r="175">
+    <row r="175" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C175" s="6"/>
       <c r="F175" s="6"/>
       <c r="I175" s="6"/>
       <c r="K175" s="6"/>
     </row>
-    <row r="176">
+    <row r="176" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C176" s="6"/>
       <c r="F176" s="6"/>
       <c r="I176" s="6"/>
       <c r="K176" s="6"/>
     </row>
-    <row r="177">
+    <row r="177" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C177" s="6"/>
       <c r="F177" s="6"/>
       <c r="I177" s="6"/>
       <c r="K177" s="6"/>
     </row>
-    <row r="178">
+    <row r="178" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C178" s="6"/>
       <c r="F178" s="6"/>
       <c r="I178" s="6"/>
       <c r="K178" s="6"/>
     </row>
-    <row r="179">
+    <row r="179" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C179" s="6"/>
       <c r="F179" s="6"/>
       <c r="I179" s="6"/>
       <c r="K179" s="6"/>
     </row>
-    <row r="180">
+    <row r="180" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C180" s="6"/>
       <c r="F180" s="6"/>
       <c r="I180" s="6"/>
       <c r="K180" s="6"/>
     </row>
-    <row r="181">
+    <row r="181" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C181" s="6"/>
       <c r="F181" s="6"/>
       <c r="I181" s="6"/>
       <c r="K181" s="6"/>
     </row>
-    <row r="182">
+    <row r="182" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C182" s="6"/>
       <c r="F182" s="6"/>
       <c r="I182" s="6"/>
       <c r="K182" s="6"/>
     </row>
-    <row r="183">
+    <row r="183" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C183" s="6"/>
       <c r="F183" s="6"/>
       <c r="I183" s="6"/>
       <c r="K183" s="6"/>
     </row>
-    <row r="184">
+    <row r="184" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C184" s="6"/>
       <c r="F184" s="6"/>
       <c r="I184" s="6"/>
       <c r="K184" s="6"/>
     </row>
-    <row r="185">
+    <row r="185" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C185" s="6"/>
       <c r="F185" s="6"/>
       <c r="I185" s="6"/>
       <c r="K185" s="6"/>
     </row>
-    <row r="186">
+    <row r="186" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C186" s="6"/>
       <c r="F186" s="6"/>
       <c r="I186" s="6"/>
       <c r="K186" s="6"/>
     </row>
-    <row r="187">
+    <row r="187" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C187" s="6"/>
       <c r="F187" s="6"/>
       <c r="I187" s="6"/>
       <c r="K187" s="6"/>
     </row>
-    <row r="188">
+    <row r="188" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C188" s="6"/>
       <c r="F188" s="6"/>
       <c r="I188" s="6"/>
       <c r="K188" s="6"/>
     </row>
-    <row r="189">
+    <row r="189" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C189" s="6"/>
       <c r="F189" s="6"/>
       <c r="I189" s="6"/>
       <c r="K189" s="6"/>
     </row>
-    <row r="190">
+    <row r="190" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C190" s="6"/>
       <c r="F190" s="6"/>
       <c r="I190" s="6"/>
       <c r="K190" s="6"/>
     </row>
-    <row r="191">
+    <row r="191" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C191" s="6"/>
       <c r="F191" s="6"/>
       <c r="I191" s="6"/>
       <c r="K191" s="6"/>
     </row>
-    <row r="192">
+    <row r="192" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C192" s="6"/>
       <c r="F192" s="6"/>
       <c r="I192" s="6"/>
       <c r="K192" s="6"/>
     </row>
-    <row r="193">
+    <row r="193" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C193" s="6"/>
       <c r="F193" s="6"/>
       <c r="I193" s="6"/>
       <c r="K193" s="6"/>
     </row>
-    <row r="194">
+    <row r="194" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C194" s="6"/>
       <c r="F194" s="6"/>
       <c r="I194" s="6"/>
       <c r="K194" s="6"/>
     </row>
-    <row r="195">
+    <row r="195" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C195" s="6"/>
       <c r="F195" s="6"/>
       <c r="I195" s="6"/>
       <c r="K195" s="6"/>
     </row>
-    <row r="196">
+    <row r="196" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C196" s="6"/>
       <c r="F196" s="6"/>
       <c r="I196" s="6"/>
       <c r="K196" s="6"/>
     </row>
-    <row r="197">
+    <row r="197" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C197" s="6"/>
       <c r="F197" s="6"/>
       <c r="I197" s="6"/>
       <c r="K197" s="6"/>
     </row>
-    <row r="198">
+    <row r="198" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C198" s="6"/>
       <c r="F198" s="6"/>
       <c r="I198" s="6"/>
       <c r="K198" s="6"/>
     </row>
-    <row r="199">
+    <row r="199" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C199" s="6"/>
       <c r="F199" s="6"/>
       <c r="I199" s="6"/>
       <c r="K199" s="6"/>
     </row>
-    <row r="200">
+    <row r="200" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C200" s="6"/>
       <c r="F200" s="6"/>
       <c r="I200" s="6"/>
       <c r="K200" s="6"/>
     </row>
-    <row r="201">
+    <row r="201" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C201" s="6"/>
       <c r="F201" s="6"/>
       <c r="I201" s="6"/>
       <c r="K201" s="6"/>
     </row>
-    <row r="202">
+    <row r="202" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C202" s="6"/>
       <c r="F202" s="6"/>
       <c r="I202" s="6"/>
       <c r="K202" s="6"/>
     </row>
-    <row r="203">
+    <row r="203" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C203" s="6"/>
       <c r="F203" s="6"/>
       <c r="I203" s="6"/>
       <c r="K203" s="6"/>
     </row>
-    <row r="204">
+    <row r="204" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C204" s="6"/>
       <c r="F204" s="6"/>
       <c r="I204" s="6"/>
       <c r="K204" s="6"/>
     </row>
-    <row r="205">
+    <row r="205" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C205" s="6"/>
       <c r="F205" s="6"/>
       <c r="I205" s="6"/>
       <c r="K205" s="6"/>
     </row>
-    <row r="206">
+    <row r="206" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C206" s="6"/>
       <c r="F206" s="6"/>
       <c r="I206" s="6"/>
       <c r="K206" s="6"/>
     </row>
-    <row r="207">
+    <row r="207" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C207" s="6"/>
       <c r="F207" s="6"/>
       <c r="I207" s="6"/>
       <c r="K207" s="6"/>
     </row>
-    <row r="208">
+    <row r="208" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C208" s="6"/>
       <c r="F208" s="6"/>
       <c r="I208" s="6"/>
       <c r="K208" s="6"/>
     </row>
-    <row r="209">
+    <row r="209" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C209" s="6"/>
       <c r="F209" s="6"/>
       <c r="I209" s="6"/>
       <c r="K209" s="6"/>
     </row>
-    <row r="210">
+    <row r="210" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C210" s="6"/>
       <c r="F210" s="6"/>
       <c r="I210" s="6"/>
       <c r="K210" s="6"/>
     </row>
-    <row r="211">
+    <row r="211" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C211" s="6"/>
       <c r="F211" s="6"/>
       <c r="I211" s="6"/>
       <c r="K211" s="6"/>
     </row>
-    <row r="212">
+    <row r="212" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C212" s="6"/>
       <c r="F212" s="6"/>
       <c r="I212" s="6"/>
       <c r="K212" s="6"/>
     </row>
-    <row r="213">
+    <row r="213" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C213" s="6"/>
       <c r="F213" s="6"/>
       <c r="I213" s="6"/>
       <c r="K213" s="6"/>
     </row>
-    <row r="214">
+    <row r="214" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C214" s="6"/>
       <c r="F214" s="6"/>
       <c r="I214" s="6"/>
       <c r="K214" s="6"/>
     </row>
-    <row r="215">
+    <row r="215" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C215" s="6"/>
       <c r="F215" s="6"/>
       <c r="I215" s="6"/>
       <c r="K215" s="6"/>
     </row>
-    <row r="216">
+    <row r="216" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C216" s="6"/>
       <c r="F216" s="6"/>
       <c r="I216" s="6"/>
       <c r="K216" s="6"/>
     </row>
-    <row r="217">
+    <row r="217" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C217" s="6"/>
       <c r="F217" s="6"/>
       <c r="I217" s="6"/>
       <c r="K217" s="6"/>
     </row>
-    <row r="218">
+    <row r="218" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C218" s="6"/>
       <c r="F218" s="6"/>
       <c r="I218" s="6"/>
       <c r="K218" s="6"/>
     </row>
-    <row r="219">
+    <row r="219" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C219" s="6"/>
       <c r="F219" s="6"/>
       <c r="I219" s="6"/>
       <c r="K219" s="6"/>
     </row>
-    <row r="220">
+    <row r="220" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C220" s="6"/>
       <c r="F220" s="6"/>
       <c r="I220" s="6"/>
       <c r="K220" s="6"/>
     </row>
-    <row r="221">
+    <row r="221" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C221" s="6"/>
       <c r="F221" s="6"/>
       <c r="I221" s="6"/>
       <c r="K221" s="6"/>
     </row>
-    <row r="222">
+    <row r="222" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C222" s="6"/>
       <c r="F222" s="6"/>
       <c r="I222" s="6"/>
       <c r="K222" s="6"/>
     </row>
-    <row r="223">
+    <row r="223" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C223" s="6"/>
       <c r="F223" s="6"/>
       <c r="I223" s="6"/>
       <c r="K223" s="6"/>
     </row>
-    <row r="224">
+    <row r="224" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C224" s="6"/>
       <c r="F224" s="6"/>
       <c r="I224" s="6"/>
       <c r="K224" s="6"/>
     </row>
-    <row r="225">
+    <row r="225" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C225" s="6"/>
       <c r="F225" s="6"/>
       <c r="I225" s="6"/>
       <c r="K225" s="6"/>
     </row>
-    <row r="226">
+    <row r="226" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C226" s="6"/>
       <c r="F226" s="6"/>
       <c r="I226" s="6"/>
       <c r="K226" s="6"/>
     </row>
-    <row r="227">
+    <row r="227" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C227" s="6"/>
       <c r="F227" s="6"/>
       <c r="I227" s="6"/>
       <c r="K227" s="6"/>
     </row>
-    <row r="228">
+    <row r="228" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C228" s="6"/>
       <c r="F228" s="6"/>
       <c r="I228" s="6"/>
       <c r="K228" s="6"/>
     </row>
-    <row r="229">
+    <row r="229" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C229" s="6"/>
       <c r="F229" s="6"/>
       <c r="I229" s="6"/>
       <c r="K229" s="6"/>
     </row>
-    <row r="230">
+    <row r="230" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C230" s="6"/>
       <c r="F230" s="6"/>
       <c r="I230" s="6"/>
       <c r="K230" s="6"/>
     </row>
-    <row r="231">
+    <row r="231" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C231" s="6"/>
       <c r="F231" s="6"/>
       <c r="I231" s="6"/>
       <c r="K231" s="6"/>
     </row>
-    <row r="232">
+    <row r="232" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C232" s="6"/>
       <c r="F232" s="6"/>
       <c r="I232" s="6"/>
       <c r="K232" s="6"/>
     </row>
-    <row r="233">
+    <row r="233" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C233" s="6"/>
       <c r="F233" s="6"/>
       <c r="I233" s="6"/>
       <c r="K233" s="6"/>
     </row>
-    <row r="234">
+    <row r="234" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C234" s="6"/>
       <c r="F234" s="6"/>
       <c r="I234" s="6"/>
       <c r="K234" s="6"/>
     </row>
-    <row r="235">
+    <row r="235" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C235" s="6"/>
       <c r="F235" s="6"/>
       <c r="I235" s="6"/>
       <c r="K235" s="6"/>
     </row>
-    <row r="236">
+    <row r="236" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C236" s="6"/>
       <c r="F236" s="6"/>
       <c r="I236" s="6"/>
       <c r="K236" s="6"/>
     </row>
-    <row r="237">
+    <row r="237" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C237" s="6"/>
       <c r="F237" s="6"/>
       <c r="I237" s="6"/>
       <c r="K237" s="6"/>
     </row>
-    <row r="238">
+    <row r="238" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C238" s="6"/>
       <c r="F238" s="6"/>
       <c r="I238" s="6"/>
       <c r="K238" s="6"/>
     </row>
-    <row r="239">
+    <row r="239" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C239" s="6"/>
       <c r="F239" s="6"/>
       <c r="I239" s="6"/>
       <c r="K239" s="6"/>
     </row>
-    <row r="240">
+    <row r="240" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C240" s="6"/>
       <c r="F240" s="6"/>
       <c r="I240" s="6"/>
       <c r="K240" s="6"/>
     </row>
-    <row r="241">
+    <row r="241" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C241" s="6"/>
       <c r="F241" s="6"/>
       <c r="I241" s="6"/>
       <c r="K241" s="6"/>
     </row>
-    <row r="242">
+    <row r="242" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C242" s="6"/>
       <c r="F242" s="6"/>
       <c r="I242" s="6"/>
       <c r="K242" s="6"/>
     </row>
-    <row r="243">
+    <row r="243" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C243" s="6"/>
       <c r="F243" s="6"/>
       <c r="I243" s="6"/>
       <c r="K243" s="6"/>
     </row>
-    <row r="244">
+    <row r="244" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C244" s="6"/>
       <c r="F244" s="6"/>
       <c r="I244" s="6"/>
       <c r="K244" s="6"/>
     </row>
-    <row r="245">
+    <row r="245" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C245" s="6"/>
       <c r="F245" s="6"/>
       <c r="I245" s="6"/>
       <c r="K245" s="6"/>
     </row>
-    <row r="246">
+    <row r="246" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C246" s="6"/>
       <c r="F246" s="6"/>
       <c r="I246" s="6"/>
       <c r="K246" s="6"/>
     </row>
-    <row r="247">
+    <row r="247" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C247" s="6"/>
       <c r="F247" s="6"/>
       <c r="I247" s="6"/>
       <c r="K247" s="6"/>
     </row>
-    <row r="248">
+    <row r="248" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C248" s="6"/>
       <c r="F248" s="6"/>
       <c r="I248" s="6"/>
       <c r="K248" s="6"/>
     </row>
-    <row r="249">
+    <row r="249" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C249" s="6"/>
       <c r="F249" s="6"/>
       <c r="I249" s="6"/>
       <c r="K249" s="6"/>
     </row>
-    <row r="250">
+    <row r="250" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C250" s="6"/>
       <c r="F250" s="6"/>
       <c r="I250" s="6"/>
       <c r="K250" s="6"/>
     </row>
-    <row r="251">
+    <row r="251" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C251" s="6"/>
       <c r="F251" s="6"/>
       <c r="I251" s="6"/>
       <c r="K251" s="6"/>
     </row>
-    <row r="252">
+    <row r="252" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C252" s="6"/>
       <c r="F252" s="6"/>
       <c r="I252" s="6"/>
       <c r="K252" s="6"/>
     </row>
-    <row r="253">
+    <row r="253" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C253" s="6"/>
       <c r="F253" s="6"/>
       <c r="I253" s="6"/>
       <c r="K253" s="6"/>
     </row>
-    <row r="254">
+    <row r="254" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C254" s="6"/>
       <c r="F254" s="6"/>
       <c r="I254" s="6"/>
       <c r="K254" s="6"/>
     </row>
-    <row r="255">
+    <row r="255" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C255" s="6"/>
       <c r="F255" s="6"/>
       <c r="I255" s="6"/>
       <c r="K255" s="6"/>
     </row>
-    <row r="256">
+    <row r="256" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C256" s="6"/>
       <c r="F256" s="6"/>
       <c r="I256" s="6"/>
       <c r="K256" s="6"/>
     </row>
-    <row r="257">
+    <row r="257" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C257" s="6"/>
       <c r="F257" s="6"/>
       <c r="I257" s="6"/>
       <c r="K257" s="6"/>
     </row>
-    <row r="258">
+    <row r="258" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C258" s="6"/>
       <c r="F258" s="6"/>
       <c r="I258" s="6"/>
       <c r="K258" s="6"/>
     </row>
-    <row r="259">
+    <row r="259" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C259" s="6"/>
       <c r="F259" s="6"/>
       <c r="I259" s="6"/>
       <c r="K259" s="6"/>
     </row>
-    <row r="260">
+    <row r="260" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C260" s="6"/>
       <c r="F260" s="6"/>
       <c r="I260" s="6"/>
       <c r="K260" s="6"/>
     </row>
-    <row r="261">
+    <row r="261" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C261" s="6"/>
       <c r="F261" s="6"/>
       <c r="I261" s="6"/>
       <c r="K261" s="6"/>
     </row>
-    <row r="262">
+    <row r="262" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C262" s="6"/>
       <c r="F262" s="6"/>
       <c r="I262" s="6"/>
       <c r="K262" s="6"/>
     </row>
-    <row r="263">
+    <row r="263" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C263" s="6"/>
       <c r="F263" s="6"/>
       <c r="I263" s="6"/>
       <c r="K263" s="6"/>
     </row>
-    <row r="264">
+    <row r="264" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C264" s="6"/>
       <c r="F264" s="6"/>
       <c r="I264" s="6"/>
       <c r="K264" s="6"/>
     </row>
-    <row r="265">
+    <row r="265" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C265" s="6"/>
       <c r="F265" s="6"/>
       <c r="I265" s="6"/>
       <c r="K265" s="6"/>
     </row>
-    <row r="266">
+    <row r="266" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C266" s="6"/>
       <c r="F266" s="6"/>
       <c r="I266" s="6"/>
       <c r="K266" s="6"/>
     </row>
-    <row r="267">
+    <row r="267" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C267" s="6"/>
       <c r="F267" s="6"/>
       <c r="I267" s="6"/>
       <c r="K267" s="6"/>
     </row>
-    <row r="268">
+    <row r="268" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C268" s="6"/>
       <c r="F268" s="6"/>
       <c r="I268" s="6"/>
       <c r="K268" s="6"/>
     </row>
-    <row r="269">
+    <row r="269" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C269" s="6"/>
       <c r="F269" s="6"/>
       <c r="I269" s="6"/>
       <c r="K269" s="6"/>
     </row>
-    <row r="270">
+    <row r="270" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C270" s="6"/>
       <c r="F270" s="6"/>
       <c r="I270" s="6"/>
       <c r="K270" s="6"/>
     </row>
-    <row r="271">
+    <row r="271" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C271" s="6"/>
       <c r="F271" s="6"/>
       <c r="I271" s="6"/>
       <c r="K271" s="6"/>
     </row>
-    <row r="272">
+    <row r="272" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C272" s="6"/>
       <c r="F272" s="6"/>
       <c r="I272" s="6"/>
       <c r="K272" s="6"/>
     </row>
-    <row r="273">
+    <row r="273" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C273" s="6"/>
       <c r="F273" s="6"/>
       <c r="I273" s="6"/>
       <c r="K273" s="6"/>
     </row>
-    <row r="274">
+    <row r="274" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C274" s="6"/>
       <c r="F274" s="6"/>
       <c r="I274" s="6"/>
       <c r="K274" s="6"/>
     </row>
-    <row r="275">
+    <row r="275" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C275" s="6"/>
       <c r="F275" s="6"/>
       <c r="I275" s="6"/>
       <c r="K275" s="6"/>
     </row>
-    <row r="276">
+    <row r="276" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C276" s="6"/>
       <c r="F276" s="6"/>
       <c r="I276" s="6"/>
       <c r="K276" s="6"/>
     </row>
-    <row r="277">
+    <row r="277" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C277" s="6"/>
       <c r="F277" s="6"/>
       <c r="I277" s="6"/>
       <c r="K277" s="6"/>
     </row>
-    <row r="278">
+    <row r="278" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C278" s="6"/>
       <c r="F278" s="6"/>
       <c r="I278" s="6"/>
       <c r="K278" s="6"/>
     </row>
-    <row r="279">
+    <row r="279" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C279" s="6"/>
       <c r="F279" s="6"/>
       <c r="I279" s="6"/>
       <c r="K279" s="6"/>
     </row>
-    <row r="280">
+    <row r="280" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C280" s="6"/>
       <c r="F280" s="6"/>
       <c r="I280" s="6"/>
       <c r="K280" s="6"/>
     </row>
-    <row r="281">
+    <row r="281" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C281" s="6"/>
       <c r="F281" s="6"/>
       <c r="I281" s="6"/>
       <c r="K281" s="6"/>
     </row>
-    <row r="282">
+    <row r="282" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C282" s="6"/>
       <c r="F282" s="6"/>
       <c r="I282" s="6"/>
       <c r="K282" s="6"/>
     </row>
-    <row r="283">
+    <row r="283" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C283" s="6"/>
       <c r="F283" s="6"/>
       <c r="I283" s="6"/>
       <c r="K283" s="6"/>
     </row>
-    <row r="284">
+    <row r="284" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C284" s="6"/>
       <c r="F284" s="6"/>
       <c r="I284" s="6"/>
       <c r="K284" s="6"/>
     </row>
-    <row r="285">
+    <row r="285" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C285" s="6"/>
       <c r="F285" s="6"/>
       <c r="I285" s="6"/>
       <c r="K285" s="6"/>
     </row>
-    <row r="286">
+    <row r="286" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C286" s="6"/>
       <c r="F286" s="6"/>
       <c r="I286" s="6"/>
       <c r="K286" s="6"/>
     </row>
-    <row r="287">
+    <row r="287" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C287" s="6"/>
       <c r="F287" s="6"/>
       <c r="I287" s="6"/>
       <c r="K287" s="6"/>
     </row>
-    <row r="288">
+    <row r="288" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C288" s="6"/>
       <c r="F288" s="6"/>
       <c r="I288" s="6"/>
       <c r="K288" s="6"/>
     </row>
-    <row r="289">
+    <row r="289" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C289" s="6"/>
       <c r="F289" s="6"/>
       <c r="I289" s="6"/>
       <c r="K289" s="6"/>
     </row>
-    <row r="290">
+    <row r="290" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C290" s="6"/>
       <c r="F290" s="6"/>
       <c r="I290" s="6"/>
       <c r="K290" s="6"/>
     </row>
-    <row r="291">
+    <row r="291" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C291" s="6"/>
       <c r="F291" s="6"/>
       <c r="I291" s="6"/>
       <c r="K291" s="6"/>
     </row>
-    <row r="292">
+    <row r="292" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C292" s="6"/>
       <c r="F292" s="6"/>
       <c r="I292" s="6"/>
       <c r="K292" s="6"/>
     </row>
-    <row r="293">
+    <row r="293" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C293" s="6"/>
       <c r="F293" s="6"/>
       <c r="I293" s="6"/>
       <c r="K293" s="6"/>
     </row>
-    <row r="294">
+    <row r="294" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C294" s="6"/>
       <c r="F294" s="6"/>
       <c r="I294" s="6"/>
       <c r="K294" s="6"/>
     </row>
-    <row r="295">
+    <row r="295" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C295" s="6"/>
       <c r="F295" s="6"/>
       <c r="I295" s="6"/>
       <c r="K295" s="6"/>
     </row>
-    <row r="296">
+    <row r="296" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C296" s="6"/>
       <c r="F296" s="6"/>
       <c r="I296" s="6"/>
       <c r="K296" s="6"/>
     </row>
-    <row r="297">
+    <row r="297" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C297" s="6"/>
       <c r="F297" s="6"/>
       <c r="I297" s="6"/>
       <c r="K297" s="6"/>
     </row>
-    <row r="298">
+    <row r="298" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C298" s="6"/>
       <c r="F298" s="6"/>
       <c r="I298" s="6"/>
       <c r="K298" s="6"/>
     </row>
-    <row r="299">
+    <row r="299" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C299" s="6"/>
       <c r="F299" s="6"/>
       <c r="I299" s="6"/>
       <c r="K299" s="6"/>
     </row>
-    <row r="300">
+    <row r="300" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C300" s="6"/>
       <c r="F300" s="6"/>
       <c r="I300" s="6"/>
       <c r="K300" s="6"/>
     </row>
-    <row r="301">
+    <row r="301" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C301" s="6"/>
       <c r="F301" s="6"/>
       <c r="I301" s="6"/>
       <c r="K301" s="6"/>
     </row>
-    <row r="302">
+    <row r="302" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C302" s="6"/>
       <c r="F302" s="6"/>
       <c r="I302" s="6"/>
       <c r="K302" s="6"/>
     </row>
-    <row r="303">
+    <row r="303" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C303" s="6"/>
       <c r="F303" s="6"/>
       <c r="I303" s="6"/>
       <c r="K303" s="6"/>
     </row>
-    <row r="304">
+    <row r="304" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C304" s="6"/>
       <c r="F304" s="6"/>
       <c r="I304" s="6"/>
       <c r="K304" s="6"/>
     </row>
-    <row r="305">
+    <row r="305" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C305" s="6"/>
       <c r="F305" s="6"/>
       <c r="I305" s="6"/>
       <c r="K305" s="6"/>
     </row>
-    <row r="306">
+    <row r="306" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C306" s="6"/>
       <c r="F306" s="6"/>
       <c r="I306" s="6"/>
       <c r="K306" s="6"/>
     </row>
-    <row r="307">
+    <row r="307" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C307" s="6"/>
       <c r="F307" s="6"/>
       <c r="I307" s="6"/>
       <c r="K307" s="6"/>
     </row>
-    <row r="308">
+    <row r="308" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C308" s="6"/>
       <c r="F308" s="6"/>
       <c r="I308" s="6"/>
       <c r="K308" s="6"/>
     </row>
-    <row r="309">
+    <row r="309" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C309" s="6"/>
       <c r="F309" s="6"/>
       <c r="I309" s="6"/>
       <c r="K309" s="6"/>
     </row>
-    <row r="310">
+    <row r="310" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C310" s="6"/>
       <c r="F310" s="6"/>
       <c r="I310" s="6"/>
       <c r="K310" s="6"/>
     </row>
-    <row r="311">
+    <row r="311" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C311" s="6"/>
       <c r="F311" s="6"/>
       <c r="I311" s="6"/>
       <c r="K311" s="6"/>
     </row>
-    <row r="312">
+    <row r="312" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C312" s="6"/>
       <c r="F312" s="6"/>
       <c r="I312" s="6"/>
       <c r="K312" s="6"/>
     </row>
-    <row r="313">
+    <row r="313" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C313" s="6"/>
       <c r="F313" s="6"/>
       <c r="I313" s="6"/>
       <c r="K313" s="6"/>
     </row>
-    <row r="314">
+    <row r="314" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C314" s="6"/>
       <c r="F314" s="6"/>
       <c r="I314" s="6"/>
       <c r="K314" s="6"/>
     </row>
-    <row r="315">
+    <row r="315" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C315" s="6"/>
       <c r="F315" s="6"/>
       <c r="I315" s="6"/>
       <c r="K315" s="6"/>
     </row>
-    <row r="316">
+    <row r="316" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C316" s="6"/>
       <c r="F316" s="6"/>
       <c r="I316" s="6"/>
       <c r="K316" s="6"/>
     </row>
-    <row r="317">
+    <row r="317" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C317" s="6"/>
       <c r="F317" s="6"/>
       <c r="I317" s="6"/>
       <c r="K317" s="6"/>
     </row>
-    <row r="318">
+    <row r="318" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C318" s="6"/>
       <c r="F318" s="6"/>
       <c r="I318" s="6"/>
       <c r="K318" s="6"/>
     </row>
-    <row r="319">
+    <row r="319" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C319" s="6"/>
       <c r="F319" s="6"/>
       <c r="I319" s="6"/>
       <c r="K319" s="6"/>
     </row>
-    <row r="320">
+    <row r="320" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C320" s="6"/>
       <c r="F320" s="6"/>
       <c r="I320" s="6"/>
       <c r="K320" s="6"/>
     </row>
-    <row r="321">
+    <row r="321" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C321" s="6"/>
       <c r="F321" s="6"/>
       <c r="I321" s="6"/>
       <c r="K321" s="6"/>
     </row>
-    <row r="322">
+    <row r="322" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C322" s="6"/>
       <c r="F322" s="6"/>
       <c r="I322" s="6"/>
       <c r="K322" s="6"/>
     </row>
-    <row r="323">
+    <row r="323" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C323" s="6"/>
       <c r="F323" s="6"/>
       <c r="I323" s="6"/>
       <c r="K323" s="6"/>
     </row>
-    <row r="324">
+    <row r="324" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C324" s="6"/>
       <c r="F324" s="6"/>
       <c r="I324" s="6"/>
       <c r="K324" s="6"/>
     </row>
-    <row r="325">
+    <row r="325" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C325" s="6"/>
       <c r="F325" s="6"/>
       <c r="I325" s="6"/>
       <c r="K325" s="6"/>
     </row>
-    <row r="326">
+    <row r="326" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C326" s="6"/>
       <c r="F326" s="6"/>
       <c r="I326" s="6"/>
       <c r="K326" s="6"/>
     </row>
-    <row r="327">
+    <row r="327" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C327" s="6"/>
       <c r="F327" s="6"/>
       <c r="I327" s="6"/>
       <c r="K327" s="6"/>
     </row>
-    <row r="328">
+    <row r="328" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C328" s="6"/>
       <c r="F328" s="6"/>
       <c r="I328" s="6"/>
       <c r="K328" s="6"/>
     </row>
-    <row r="329">
+    <row r="329" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C329" s="6"/>
       <c r="F329" s="6"/>
       <c r="I329" s="6"/>
       <c r="K329" s="6"/>
     </row>
-    <row r="330">
+    <row r="330" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C330" s="6"/>
       <c r="F330" s="6"/>
       <c r="I330" s="6"/>
       <c r="K330" s="6"/>
     </row>
-    <row r="331">
+    <row r="331" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C331" s="6"/>
       <c r="F331" s="6"/>
       <c r="I331" s="6"/>
       <c r="K331" s="6"/>
     </row>
-    <row r="332">
+    <row r="332" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C332" s="6"/>
       <c r="F332" s="6"/>
       <c r="I332" s="6"/>
       <c r="K332" s="6"/>
     </row>
-    <row r="333">
+    <row r="333" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C333" s="6"/>
       <c r="F333" s="6"/>
       <c r="I333" s="6"/>
       <c r="K333" s="6"/>
     </row>
-    <row r="334">
+    <row r="334" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C334" s="6"/>
       <c r="F334" s="6"/>
       <c r="I334" s="6"/>
       <c r="K334" s="6"/>
     </row>
-    <row r="335">
+    <row r="335" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C335" s="6"/>
       <c r="F335" s="6"/>
       <c r="I335" s="6"/>
       <c r="K335" s="6"/>
     </row>
-    <row r="336">
+    <row r="336" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C336" s="6"/>
       <c r="F336" s="6"/>
       <c r="I336" s="6"/>
       <c r="K336" s="6"/>
     </row>
-    <row r="337">
+    <row r="337" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C337" s="6"/>
       <c r="F337" s="6"/>
       <c r="I337" s="6"/>
       <c r="K337" s="6"/>
     </row>
-    <row r="338">
+    <row r="338" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C338" s="6"/>
       <c r="F338" s="6"/>
       <c r="I338" s="6"/>
       <c r="K338" s="6"/>
     </row>
-    <row r="339">
+    <row r="339" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C339" s="6"/>
       <c r="F339" s="6"/>
       <c r="I339" s="6"/>
       <c r="K339" s="6"/>
     </row>
-    <row r="340">
+    <row r="340" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C340" s="6"/>
       <c r="F340" s="6"/>
       <c r="I340" s="6"/>
       <c r="K340" s="6"/>
     </row>
-    <row r="341">
+    <row r="341" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C341" s="6"/>
       <c r="F341" s="6"/>
       <c r="I341" s="6"/>
       <c r="K341" s="6"/>
     </row>
-    <row r="342">
+    <row r="342" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C342" s="6"/>
       <c r="F342" s="6"/>
       <c r="I342" s="6"/>
       <c r="K342" s="6"/>
     </row>
-    <row r="343">
+    <row r="343" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C343" s="6"/>
       <c r="F343" s="6"/>
       <c r="I343" s="6"/>
       <c r="K343" s="6"/>
     </row>
-    <row r="344">
+    <row r="344" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C344" s="6"/>
       <c r="F344" s="6"/>
       <c r="I344" s="6"/>
       <c r="K344" s="6"/>
     </row>
-    <row r="345">
+    <row r="345" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C345" s="6"/>
       <c r="F345" s="6"/>
       <c r="I345" s="6"/>
       <c r="K345" s="6"/>
     </row>
-    <row r="346">
+    <row r="346" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C346" s="6"/>
       <c r="F346" s="6"/>
       <c r="I346" s="6"/>
       <c r="K346" s="6"/>
     </row>
-    <row r="347">
+    <row r="347" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C347" s="6"/>
       <c r="F347" s="6"/>
       <c r="I347" s="6"/>
       <c r="K347" s="6"/>
     </row>
-    <row r="348">
+    <row r="348" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C348" s="6"/>
       <c r="F348" s="6"/>
       <c r="I348" s="6"/>
       <c r="K348" s="6"/>
     </row>
-    <row r="349">
+    <row r="349" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C349" s="6"/>
       <c r="F349" s="6"/>
       <c r="I349" s="6"/>
       <c r="K349" s="6"/>
     </row>
-    <row r="350">
+    <row r="350" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C350" s="6"/>
       <c r="F350" s="6"/>
       <c r="I350" s="6"/>
       <c r="K350" s="6"/>
     </row>
-    <row r="351">
+    <row r="351" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C351" s="6"/>
       <c r="F351" s="6"/>
       <c r="I351" s="6"/>
       <c r="K351" s="6"/>
     </row>
-    <row r="352">
+    <row r="352" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C352" s="6"/>
       <c r="F352" s="6"/>
       <c r="I352" s="6"/>
       <c r="K352" s="6"/>
     </row>
-    <row r="353">
+    <row r="353" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C353" s="6"/>
       <c r="F353" s="6"/>
       <c r="I353" s="6"/>
       <c r="K353" s="6"/>
     </row>
-    <row r="354">
+    <row r="354" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C354" s="6"/>
       <c r="F354" s="6"/>
       <c r="I354" s="6"/>
       <c r="K354" s="6"/>
     </row>
-    <row r="355">
+    <row r="355" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C355" s="6"/>
       <c r="F355" s="6"/>
       <c r="I355" s="6"/>
       <c r="K355" s="6"/>
     </row>
-    <row r="356">
+    <row r="356" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C356" s="6"/>
       <c r="F356" s="6"/>
       <c r="I356" s="6"/>
       <c r="K356" s="6"/>
     </row>
-    <row r="357">
+    <row r="357" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C357" s="6"/>
       <c r="F357" s="6"/>
       <c r="I357" s="6"/>
       <c r="K357" s="6"/>
     </row>
-    <row r="358">
+    <row r="358" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C358" s="6"/>
       <c r="F358" s="6"/>
       <c r="I358" s="6"/>
       <c r="K358" s="6"/>
     </row>
-    <row r="359">
+    <row r="359" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C359" s="6"/>
       <c r="F359" s="6"/>
       <c r="I359" s="6"/>
       <c r="K359" s="6"/>
     </row>
-    <row r="360">
+    <row r="360" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C360" s="6"/>
       <c r="F360" s="6"/>
       <c r="I360" s="6"/>
       <c r="K360" s="6"/>
     </row>
-    <row r="361">
+    <row r="361" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C361" s="6"/>
       <c r="F361" s="6"/>
       <c r="I361" s="6"/>
       <c r="K361" s="6"/>
     </row>
-    <row r="362">
+    <row r="362" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C362" s="6"/>
       <c r="F362" s="6"/>
       <c r="I362" s="6"/>
       <c r="K362" s="6"/>
     </row>
-    <row r="363">
+    <row r="363" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C363" s="6"/>
       <c r="F363" s="6"/>
       <c r="I363" s="6"/>
       <c r="K363" s="6"/>
     </row>
-    <row r="364">
+    <row r="364" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C364" s="6"/>
       <c r="F364" s="6"/>
       <c r="I364" s="6"/>
       <c r="K364" s="6"/>
     </row>
-    <row r="365">
+    <row r="365" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C365" s="6"/>
       <c r="F365" s="6"/>
       <c r="I365" s="6"/>
       <c r="K365" s="6"/>
     </row>
-    <row r="366">
+    <row r="366" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C366" s="6"/>
       <c r="F366" s="6"/>
       <c r="I366" s="6"/>
       <c r="K366" s="6"/>
     </row>
-    <row r="367">
+    <row r="367" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C367" s="6"/>
       <c r="F367" s="6"/>
       <c r="I367" s="6"/>
       <c r="K367" s="6"/>
     </row>
-    <row r="368">
+    <row r="368" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C368" s="6"/>
       <c r="F368" s="6"/>
       <c r="I368" s="6"/>
       <c r="K368" s="6"/>
     </row>
-    <row r="369">
+    <row r="369" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C369" s="6"/>
       <c r="F369" s="6"/>
       <c r="I369" s="6"/>
       <c r="K369" s="6"/>
     </row>
-    <row r="370">
+    <row r="370" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C370" s="6"/>
       <c r="F370" s="6"/>
       <c r="I370" s="6"/>
       <c r="K370" s="6"/>
     </row>
-    <row r="371">
+    <row r="371" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C371" s="6"/>
       <c r="F371" s="6"/>
       <c r="I371" s="6"/>
       <c r="K371" s="6"/>
     </row>
-    <row r="372">
+    <row r="372" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C372" s="6"/>
       <c r="F372" s="6"/>
       <c r="I372" s="6"/>
       <c r="K372" s="6"/>
     </row>
-    <row r="373">
+    <row r="373" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C373" s="6"/>
       <c r="F373" s="6"/>
       <c r="I373" s="6"/>
       <c r="K373" s="6"/>
     </row>
-    <row r="374">
+    <row r="374" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C374" s="6"/>
       <c r="F374" s="6"/>
       <c r="I374" s="6"/>
       <c r="K374" s="6"/>
     </row>
-    <row r="375">
+    <row r="375" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C375" s="6"/>
       <c r="F375" s="6"/>
       <c r="I375" s="6"/>
       <c r="K375" s="6"/>
     </row>
-    <row r="376">
+    <row r="376" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C376" s="6"/>
       <c r="F376" s="6"/>
       <c r="I376" s="6"/>
       <c r="K376" s="6"/>
     </row>
-    <row r="377">
+    <row r="377" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C377" s="6"/>
       <c r="F377" s="6"/>
       <c r="I377" s="6"/>
       <c r="K377" s="6"/>
     </row>
-    <row r="378">
+    <row r="378" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C378" s="6"/>
       <c r="F378" s="6"/>
       <c r="I378" s="6"/>
       <c r="K378" s="6"/>
     </row>
-    <row r="379">
+    <row r="379" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C379" s="6"/>
       <c r="F379" s="6"/>
       <c r="I379" s="6"/>
       <c r="K379" s="6"/>
     </row>
-    <row r="380">
+    <row r="380" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C380" s="6"/>
       <c r="F380" s="6"/>
       <c r="I380" s="6"/>
       <c r="K380" s="6"/>
     </row>
-    <row r="381">
+    <row r="381" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C381" s="6"/>
       <c r="F381" s="6"/>
       <c r="I381" s="6"/>
       <c r="K381" s="6"/>
     </row>
-    <row r="382">
+    <row r="382" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C382" s="6"/>
       <c r="F382" s="6"/>
       <c r="I382" s="6"/>
       <c r="K382" s="6"/>
     </row>
-    <row r="383">
+    <row r="383" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C383" s="6"/>
       <c r="F383" s="6"/>
       <c r="I383" s="6"/>
       <c r="K383" s="6"/>
     </row>
-    <row r="384">
+    <row r="384" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C384" s="6"/>
       <c r="F384" s="6"/>
       <c r="I384" s="6"/>
       <c r="K384" s="6"/>
     </row>
-    <row r="385">
+    <row r="385" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C385" s="6"/>
       <c r="F385" s="6"/>
       <c r="I385" s="6"/>
       <c r="K385" s="6"/>
     </row>
-    <row r="386">
+    <row r="386" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C386" s="6"/>
       <c r="F386" s="6"/>
       <c r="I386" s="6"/>
       <c r="K386" s="6"/>
     </row>
-    <row r="387">
+    <row r="387" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C387" s="6"/>
       <c r="F387" s="6"/>
       <c r="I387" s="6"/>
       <c r="K387" s="6"/>
     </row>
-    <row r="388">
+    <row r="388" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C388" s="6"/>
       <c r="F388" s="6"/>
       <c r="I388" s="6"/>
       <c r="K388" s="6"/>
     </row>
-    <row r="389">
+    <row r="389" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C389" s="6"/>
       <c r="F389" s="6"/>
       <c r="I389" s="6"/>
       <c r="K389" s="6"/>
     </row>
-    <row r="390">
+    <row r="390" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C390" s="6"/>
       <c r="F390" s="6"/>
       <c r="I390" s="6"/>
       <c r="K390" s="6"/>
     </row>
-    <row r="391">
+    <row r="391" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C391" s="6"/>
       <c r="F391" s="6"/>
       <c r="I391" s="6"/>
       <c r="K391" s="6"/>
     </row>
-    <row r="392">
+    <row r="392" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C392" s="6"/>
       <c r="F392" s="6"/>
       <c r="I392" s="6"/>
       <c r="K392" s="6"/>
     </row>
-    <row r="393">
+    <row r="393" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C393" s="6"/>
       <c r="F393" s="6"/>
       <c r="I393" s="6"/>
       <c r="K393" s="6"/>
     </row>
-    <row r="394">
+    <row r="394" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C394" s="6"/>
       <c r="F394" s="6"/>
       <c r="I394" s="6"/>
       <c r="K394" s="6"/>
     </row>
-    <row r="395">
+    <row r="395" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C395" s="6"/>
       <c r="F395" s="6"/>
       <c r="I395" s="6"/>
       <c r="K395" s="6"/>
     </row>
-    <row r="396">
+    <row r="396" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C396" s="6"/>
       <c r="F396" s="6"/>
       <c r="I396" s="6"/>
       <c r="K396" s="6"/>
     </row>
-    <row r="397">
+    <row r="397" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C397" s="6"/>
       <c r="F397" s="6"/>
       <c r="I397" s="6"/>
       <c r="K397" s="6"/>
     </row>
-    <row r="398">
+    <row r="398" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C398" s="6"/>
       <c r="F398" s="6"/>
       <c r="I398" s="6"/>
       <c r="K398" s="6"/>
     </row>
-    <row r="399">
+    <row r="399" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C399" s="6"/>
       <c r="F399" s="6"/>
       <c r="I399" s="6"/>
       <c r="K399" s="6"/>
     </row>
-    <row r="400">
+    <row r="400" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C400" s="6"/>
       <c r="F400" s="6"/>
       <c r="I400" s="6"/>
       <c r="K400" s="6"/>
     </row>
-    <row r="401">
+    <row r="401" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C401" s="6"/>
       <c r="F401" s="6"/>
       <c r="I401" s="6"/>
       <c r="K401" s="6"/>
     </row>
-    <row r="402">
+    <row r="402" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C402" s="6"/>
       <c r="F402" s="6"/>
       <c r="I402" s="6"/>
       <c r="K402" s="6"/>
     </row>
-    <row r="403">
+    <row r="403" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C403" s="6"/>
       <c r="F403" s="6"/>
       <c r="I403" s="6"/>
       <c r="K403" s="6"/>
     </row>
-    <row r="404">
+    <row r="404" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C404" s="6"/>
       <c r="F404" s="6"/>
       <c r="I404" s="6"/>
       <c r="K404" s="6"/>
     </row>
-    <row r="405">
+    <row r="405" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C405" s="6"/>
       <c r="F405" s="6"/>
       <c r="I405" s="6"/>
       <c r="K405" s="6"/>
     </row>
-    <row r="406">
+    <row r="406" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C406" s="6"/>
       <c r="F406" s="6"/>
       <c r="I406" s="6"/>
       <c r="K406" s="6"/>
     </row>
-    <row r="407">
+    <row r="407" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C407" s="6"/>
       <c r="F407" s="6"/>
       <c r="I407" s="6"/>
       <c r="K407" s="6"/>
     </row>
-    <row r="408">
+    <row r="408" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C408" s="6"/>
       <c r="F408" s="6"/>
       <c r="I408" s="6"/>
       <c r="K408" s="6"/>
     </row>
-    <row r="409">
+    <row r="409" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C409" s="6"/>
       <c r="F409" s="6"/>
       <c r="I409" s="6"/>
       <c r="K409" s="6"/>
     </row>
-    <row r="410">
+    <row r="410" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C410" s="6"/>
       <c r="F410" s="6"/>
       <c r="I410" s="6"/>
       <c r="K410" s="6"/>
     </row>
-    <row r="411">
+    <row r="411" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C411" s="6"/>
       <c r="F411" s="6"/>
       <c r="I411" s="6"/>
       <c r="K411" s="6"/>
     </row>
-    <row r="412">
+    <row r="412" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C412" s="6"/>
       <c r="F412" s="6"/>
       <c r="I412" s="6"/>
       <c r="K412" s="6"/>
     </row>
-    <row r="413">
+    <row r="413" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C413" s="6"/>
       <c r="F413" s="6"/>
       <c r="I413" s="6"/>
       <c r="K413" s="6"/>
     </row>
-    <row r="414">
+    <row r="414" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C414" s="6"/>
       <c r="F414" s="6"/>
       <c r="I414" s="6"/>
       <c r="K414" s="6"/>
     </row>
-    <row r="415">
+    <row r="415" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C415" s="6"/>
       <c r="F415" s="6"/>
       <c r="I415" s="6"/>
       <c r="K415" s="6"/>
     </row>
-    <row r="416">
+    <row r="416" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C416" s="6"/>
       <c r="F416" s="6"/>
       <c r="I416" s="6"/>
       <c r="K416" s="6"/>
     </row>
-    <row r="417">
+    <row r="417" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C417" s="6"/>
       <c r="F417" s="6"/>
       <c r="I417" s="6"/>
       <c r="K417" s="6"/>
     </row>
-    <row r="418">
+    <row r="418" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C418" s="6"/>
       <c r="F418" s="6"/>
       <c r="I418" s="6"/>
       <c r="K418" s="6"/>
     </row>
-    <row r="419">
+    <row r="419" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C419" s="6"/>
       <c r="F419" s="6"/>
       <c r="I419" s="6"/>
       <c r="K419" s="6"/>
     </row>
-    <row r="420">
+    <row r="420" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C420" s="6"/>
       <c r="F420" s="6"/>
       <c r="I420" s="6"/>
       <c r="K420" s="6"/>
     </row>
-    <row r="421">
+    <row r="421" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C421" s="6"/>
       <c r="F421" s="6"/>
       <c r="I421" s="6"/>
       <c r="K421" s="6"/>
     </row>
-    <row r="422">
+    <row r="422" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C422" s="6"/>
       <c r="F422" s="6"/>
       <c r="I422" s="6"/>
       <c r="K422" s="6"/>
     </row>
-    <row r="423">
+    <row r="423" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C423" s="6"/>
       <c r="F423" s="6"/>
       <c r="I423" s="6"/>
       <c r="K423" s="6"/>
     </row>
-    <row r="424">
+    <row r="424" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C424" s="6"/>
       <c r="F424" s="6"/>
       <c r="I424" s="6"/>
       <c r="K424" s="6"/>
     </row>
-    <row r="425">
+    <row r="425" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C425" s="6"/>
       <c r="F425" s="6"/>
       <c r="I425" s="6"/>
       <c r="K425" s="6"/>
     </row>
-    <row r="426">
+    <row r="426" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C426" s="6"/>
       <c r="F426" s="6"/>
       <c r="I426" s="6"/>
       <c r="K426" s="6"/>
     </row>
-    <row r="427">
+    <row r="427" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C427" s="6"/>
       <c r="F427" s="6"/>
       <c r="I427" s="6"/>
       <c r="K427" s="6"/>
     </row>
-    <row r="428">
+    <row r="428" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C428" s="6"/>
       <c r="F428" s="6"/>
       <c r="I428" s="6"/>
       <c r="K428" s="6"/>
     </row>
-    <row r="429">
+    <row r="429" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C429" s="6"/>
       <c r="F429" s="6"/>
       <c r="I429" s="6"/>
       <c r="K429" s="6"/>
     </row>
-    <row r="430">
+    <row r="430" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C430" s="6"/>
       <c r="F430" s="6"/>
       <c r="I430" s="6"/>
       <c r="K430" s="6"/>
     </row>
-    <row r="431">
+    <row r="431" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C431" s="6"/>
       <c r="F431" s="6"/>
       <c r="I431" s="6"/>
       <c r="K431" s="6"/>
     </row>
-    <row r="432">
+    <row r="432" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C432" s="6"/>
       <c r="F432" s="6"/>
       <c r="I432" s="6"/>
       <c r="K432" s="6"/>
     </row>
-    <row r="433">
+    <row r="433" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C433" s="6"/>
       <c r="F433" s="6"/>
       <c r="I433" s="6"/>
       <c r="K433" s="6"/>
     </row>
-    <row r="434">
+    <row r="434" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C434" s="6"/>
       <c r="F434" s="6"/>
       <c r="I434" s="6"/>
       <c r="K434" s="6"/>
     </row>
-    <row r="435">
+    <row r="435" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C435" s="6"/>
       <c r="F435" s="6"/>
       <c r="I435" s="6"/>
       <c r="K435" s="6"/>
     </row>
-    <row r="436">
+    <row r="436" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C436" s="6"/>
       <c r="F436" s="6"/>
       <c r="I436" s="6"/>
       <c r="K436" s="6"/>
     </row>
-    <row r="437">
+    <row r="437" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C437" s="6"/>
       <c r="F437" s="6"/>
       <c r="I437" s="6"/>
       <c r="K437" s="6"/>
     </row>
-    <row r="438">
+    <row r="438" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C438" s="6"/>
       <c r="F438" s="6"/>
       <c r="I438" s="6"/>
       <c r="K438" s="6"/>
     </row>
-    <row r="439">
+    <row r="439" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C439" s="6"/>
       <c r="F439" s="6"/>
       <c r="I439" s="6"/>
       <c r="K439" s="6"/>
     </row>
-    <row r="440">
+    <row r="440" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C440" s="6"/>
       <c r="F440" s="6"/>
       <c r="I440" s="6"/>
       <c r="K440" s="6"/>
     </row>
-    <row r="441">
+    <row r="441" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C441" s="6"/>
       <c r="F441" s="6"/>
       <c r="I441" s="6"/>
       <c r="K441" s="6"/>
     </row>
-    <row r="442">
+    <row r="442" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C442" s="6"/>
       <c r="F442" s="6"/>
       <c r="I442" s="6"/>
       <c r="K442" s="6"/>
     </row>
-    <row r="443">
+    <row r="443" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C443" s="6"/>
       <c r="F443" s="6"/>
       <c r="I443" s="6"/>
       <c r="K443" s="6"/>
     </row>
-    <row r="444">
+    <row r="444" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C444" s="6"/>
       <c r="F444" s="6"/>
       <c r="I444" s="6"/>
       <c r="K444" s="6"/>
     </row>
-    <row r="445">
+    <row r="445" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C445" s="6"/>
       <c r="F445" s="6"/>
       <c r="I445" s="6"/>
       <c r="K445" s="6"/>
     </row>
-    <row r="446">
+    <row r="446" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C446" s="6"/>
       <c r="F446" s="6"/>
       <c r="I446" s="6"/>
       <c r="K446" s="6"/>
     </row>
-    <row r="447">
+    <row r="447" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C447" s="6"/>
       <c r="F447" s="6"/>
       <c r="I447" s="6"/>
       <c r="K447" s="6"/>
     </row>
-    <row r="448">
+    <row r="448" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C448" s="6"/>
       <c r="F448" s="6"/>
       <c r="I448" s="6"/>
       <c r="K448" s="6"/>
     </row>
-    <row r="449">
+    <row r="449" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C449" s="6"/>
       <c r="F449" s="6"/>
       <c r="I449" s="6"/>
       <c r="K449" s="6"/>
     </row>
-    <row r="450">
+    <row r="450" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C450" s="6"/>
       <c r="F450" s="6"/>
       <c r="I450" s="6"/>
       <c r="K450" s="6"/>
     </row>
-    <row r="451">
+    <row r="451" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C451" s="6"/>
       <c r="F451" s="6"/>
       <c r="I451" s="6"/>
       <c r="K451" s="6"/>
     </row>
-    <row r="452">
+    <row r="452" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C452" s="6"/>
       <c r="F452" s="6"/>
       <c r="I452" s="6"/>
       <c r="K452" s="6"/>
     </row>
-    <row r="453">
+    <row r="453" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C453" s="6"/>
       <c r="F453" s="6"/>
       <c r="I453" s="6"/>
       <c r="K453" s="6"/>
     </row>
-    <row r="454">
+    <row r="454" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C454" s="6"/>
       <c r="F454" s="6"/>
       <c r="I454" s="6"/>
       <c r="K454" s="6"/>
     </row>
-    <row r="455">
+    <row r="455" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C455" s="6"/>
       <c r="F455" s="6"/>
       <c r="I455" s="6"/>
       <c r="K455" s="6"/>
     </row>
-    <row r="456">
+    <row r="456" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C456" s="6"/>
       <c r="F456" s="6"/>
       <c r="I456" s="6"/>
       <c r="K456" s="6"/>
     </row>
-    <row r="457">
+    <row r="457" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C457" s="6"/>
       <c r="F457" s="6"/>
       <c r="I457" s="6"/>
       <c r="K457" s="6"/>
     </row>
-    <row r="458">
+    <row r="458" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C458" s="6"/>
       <c r="F458" s="6"/>
       <c r="I458" s="6"/>
       <c r="K458" s="6"/>
     </row>
-    <row r="459">
+    <row r="459" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C459" s="6"/>
       <c r="F459" s="6"/>
       <c r="I459" s="6"/>
       <c r="K459" s="6"/>
     </row>
-    <row r="460">
+    <row r="460" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C460" s="6"/>
       <c r="F460" s="6"/>
       <c r="I460" s="6"/>
       <c r="K460" s="6"/>
     </row>
-    <row r="461">
+    <row r="461" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C461" s="6"/>
       <c r="F461" s="6"/>
       <c r="I461" s="6"/>
       <c r="K461" s="6"/>
     </row>
-    <row r="462">
+    <row r="462" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C462" s="6"/>
       <c r="F462" s="6"/>
       <c r="I462" s="6"/>
       <c r="K462" s="6"/>
     </row>
-    <row r="463">
+    <row r="463" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C463" s="6"/>
       <c r="F463" s="6"/>
       <c r="I463" s="6"/>
       <c r="K463" s="6"/>
     </row>
-    <row r="464">
+    <row r="464" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C464" s="6"/>
       <c r="F464" s="6"/>
       <c r="I464" s="6"/>
       <c r="K464" s="6"/>
     </row>
-    <row r="465">
+    <row r="465" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C465" s="6"/>
       <c r="F465" s="6"/>
       <c r="I465" s="6"/>
       <c r="K465" s="6"/>
     </row>
-    <row r="466">
+    <row r="466" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C466" s="6"/>
       <c r="F466" s="6"/>
       <c r="I466" s="6"/>
       <c r="K466" s="6"/>
     </row>
-    <row r="467">
+    <row r="467" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C467" s="6"/>
       <c r="F467" s="6"/>
       <c r="I467" s="6"/>
       <c r="K467" s="6"/>
     </row>
-    <row r="468">
+    <row r="468" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C468" s="6"/>
       <c r="F468" s="6"/>
       <c r="I468" s="6"/>
       <c r="K468" s="6"/>
     </row>
-    <row r="469">
+    <row r="469" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C469" s="6"/>
       <c r="F469" s="6"/>
       <c r="I469" s="6"/>
       <c r="K469" s="6"/>
     </row>
-    <row r="470">
+    <row r="470" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C470" s="6"/>
       <c r="F470" s="6"/>
       <c r="I470" s="6"/>
       <c r="K470" s="6"/>
     </row>
-    <row r="471">
+    <row r="471" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C471" s="6"/>
       <c r="F471" s="6"/>
       <c r="I471" s="6"/>
       <c r="K471" s="6"/>
     </row>
-    <row r="472">
+    <row r="472" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C472" s="6"/>
       <c r="F472" s="6"/>
       <c r="I472" s="6"/>
       <c r="K472" s="6"/>
     </row>
-    <row r="473">
+    <row r="473" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C473" s="6"/>
       <c r="F473" s="6"/>
       <c r="I473" s="6"/>
       <c r="K473" s="6"/>
     </row>
-    <row r="474">
+    <row r="474" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C474" s="6"/>
       <c r="F474" s="6"/>
       <c r="I474" s="6"/>
       <c r="K474" s="6"/>
     </row>
-    <row r="475">
+    <row r="475" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C475" s="6"/>
       <c r="F475" s="6"/>
       <c r="I475" s="6"/>
       <c r="K475" s="6"/>
     </row>
-    <row r="476">
+    <row r="476" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C476" s="6"/>
       <c r="F476" s="6"/>
       <c r="I476" s="6"/>
       <c r="K476" s="6"/>
     </row>
-    <row r="477">
+    <row r="477" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C477" s="6"/>
       <c r="F477" s="6"/>
       <c r="I477" s="6"/>
       <c r="K477" s="6"/>
     </row>
-    <row r="478">
+    <row r="478" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C478" s="6"/>
       <c r="F478" s="6"/>
       <c r="I478" s="6"/>
       <c r="K478" s="6"/>
     </row>
-    <row r="479">
+    <row r="479" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C479" s="6"/>
       <c r="F479" s="6"/>
       <c r="I479" s="6"/>
       <c r="K479" s="6"/>
     </row>
-    <row r="480">
+    <row r="480" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C480" s="6"/>
       <c r="F480" s="6"/>
       <c r="I480" s="6"/>
       <c r="K480" s="6"/>
     </row>
-    <row r="481">
+    <row r="481" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C481" s="6"/>
       <c r="F481" s="6"/>
       <c r="I481" s="6"/>
       <c r="K481" s="6"/>
     </row>
-    <row r="482">
+    <row r="482" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C482" s="6"/>
       <c r="F482" s="6"/>
       <c r="I482" s="6"/>
       <c r="K482" s="6"/>
     </row>
-    <row r="483">
+    <row r="483" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C483" s="6"/>
       <c r="F483" s="6"/>
       <c r="I483" s="6"/>
       <c r="K483" s="6"/>
     </row>
-    <row r="484">
+    <row r="484" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C484" s="6"/>
       <c r="F484" s="6"/>
       <c r="I484" s="6"/>
       <c r="K484" s="6"/>
     </row>
-    <row r="485">
+    <row r="485" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C485" s="6"/>
       <c r="F485" s="6"/>
       <c r="I485" s="6"/>
       <c r="K485" s="6"/>
     </row>
-    <row r="486">
+    <row r="486" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C486" s="6"/>
       <c r="F486" s="6"/>
       <c r="I486" s="6"/>
       <c r="K486" s="6"/>
     </row>
-    <row r="487">
+    <row r="487" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C487" s="6"/>
       <c r="F487" s="6"/>
       <c r="I487" s="6"/>
       <c r="K487" s="6"/>
     </row>
-    <row r="488">
+    <row r="488" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C488" s="6"/>
       <c r="F488" s="6"/>
       <c r="I488" s="6"/>
       <c r="K488" s="6"/>
     </row>
-    <row r="489">
+    <row r="489" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C489" s="6"/>
       <c r="F489" s="6"/>
       <c r="I489" s="6"/>
       <c r="K489" s="6"/>
     </row>
-    <row r="490">
+    <row r="490" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C490" s="6"/>
       <c r="F490" s="6"/>
       <c r="I490" s="6"/>
       <c r="K490" s="6"/>
     </row>
-    <row r="491">
+    <row r="491" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C491" s="6"/>
       <c r="F491" s="6"/>
       <c r="I491" s="6"/>
       <c r="K491" s="6"/>
     </row>
-    <row r="492">
+    <row r="492" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C492" s="6"/>
       <c r="F492" s="6"/>
       <c r="I492" s="6"/>
       <c r="K492" s="6"/>
     </row>
-    <row r="493">
+    <row r="493" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C493" s="6"/>
       <c r="F493" s="6"/>
       <c r="I493" s="6"/>
       <c r="K493" s="6"/>
     </row>
-    <row r="494">
+    <row r="494" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C494" s="6"/>
       <c r="F494" s="6"/>
       <c r="I494" s="6"/>
       <c r="K494" s="6"/>
     </row>
-    <row r="495">
+    <row r="495" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C495" s="6"/>
       <c r="F495" s="6"/>
       <c r="I495" s="6"/>
       <c r="K495" s="6"/>
     </row>
-    <row r="496">
+    <row r="496" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C496" s="6"/>
       <c r="F496" s="6"/>
       <c r="I496" s="6"/>
       <c r="K496" s="6"/>
     </row>
-    <row r="497">
+    <row r="497" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C497" s="6"/>
       <c r="F497" s="6"/>
       <c r="I497" s="6"/>
       <c r="K497" s="6"/>
     </row>
-    <row r="498">
+    <row r="498" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C498" s="6"/>
       <c r="F498" s="6"/>
       <c r="I498" s="6"/>
       <c r="K498" s="6"/>
     </row>
-    <row r="499">
+    <row r="499" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C499" s="6"/>
       <c r="F499" s="6"/>
       <c r="I499" s="6"/>
       <c r="K499" s="6"/>
     </row>
-    <row r="500">
+    <row r="500" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C500" s="6"/>
       <c r="F500" s="6"/>
       <c r="I500" s="6"/>
       <c r="K500" s="6"/>
     </row>
-    <row r="501">
+    <row r="501" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C501" s="6"/>
       <c r="F501" s="6"/>
       <c r="I501" s="6"/>
       <c r="K501" s="6"/>
     </row>
-    <row r="502">
+    <row r="502" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C502" s="6"/>
       <c r="F502" s="6"/>
       <c r="I502" s="6"/>
       <c r="K502" s="6"/>
     </row>
-    <row r="503">
+    <row r="503" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C503" s="6"/>
       <c r="F503" s="6"/>
       <c r="I503" s="6"/>
       <c r="K503" s="6"/>
     </row>
-    <row r="504">
+    <row r="504" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C504" s="6"/>
       <c r="F504" s="6"/>
       <c r="I504" s="6"/>
       <c r="K504" s="6"/>
     </row>
-    <row r="505">
+    <row r="505" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C505" s="6"/>
       <c r="F505" s="6"/>
       <c r="I505" s="6"/>
       <c r="K505" s="6"/>
     </row>
-    <row r="506">
+    <row r="506" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C506" s="6"/>
       <c r="F506" s="6"/>
       <c r="I506" s="6"/>
       <c r="K506" s="6"/>
     </row>
-    <row r="507">
+    <row r="507" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C507" s="6"/>
       <c r="F507" s="6"/>
       <c r="I507" s="6"/>
       <c r="K507" s="6"/>
     </row>
-    <row r="508">
+    <row r="508" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C508" s="6"/>
       <c r="F508" s="6"/>
       <c r="I508" s="6"/>
       <c r="K508" s="6"/>
     </row>
-    <row r="509">
+    <row r="509" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C509" s="6"/>
       <c r="F509" s="6"/>
       <c r="I509" s="6"/>
       <c r="K509" s="6"/>
     </row>
-    <row r="510">
+    <row r="510" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C510" s="6"/>
       <c r="F510" s="6"/>
       <c r="I510" s="6"/>
       <c r="K510" s="6"/>
     </row>
-    <row r="511">
+    <row r="511" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C511" s="6"/>
       <c r="F511" s="6"/>
       <c r="I511" s="6"/>
       <c r="K511" s="6"/>
     </row>
-    <row r="512">
+    <row r="512" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C512" s="6"/>
       <c r="F512" s="6"/>
       <c r="I512" s="6"/>
       <c r="K512" s="6"/>
     </row>
-    <row r="513">
+    <row r="513" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C513" s="6"/>
       <c r="F513" s="6"/>
       <c r="I513" s="6"/>
       <c r="K513" s="6"/>
     </row>
-    <row r="514">
+    <row r="514" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C514" s="6"/>
       <c r="F514" s="6"/>
       <c r="I514" s="6"/>
       <c r="K514" s="6"/>
     </row>
-    <row r="515">
+    <row r="515" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C515" s="6"/>
       <c r="F515" s="6"/>
       <c r="I515" s="6"/>
       <c r="K515" s="6"/>
     </row>
-    <row r="516">
+    <row r="516" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C516" s="6"/>
       <c r="F516" s="6"/>
       <c r="I516" s="6"/>
       <c r="K516" s="6"/>
     </row>
-    <row r="517">
+    <row r="517" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C517" s="6"/>
       <c r="F517" s="6"/>
       <c r="I517" s="6"/>
       <c r="K517" s="6"/>
     </row>
-    <row r="518">
+    <row r="518" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C518" s="6"/>
       <c r="F518" s="6"/>
       <c r="I518" s="6"/>
       <c r="K518" s="6"/>
     </row>
-    <row r="519">
+    <row r="519" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C519" s="6"/>
       <c r="F519" s="6"/>
       <c r="I519" s="6"/>
       <c r="K519" s="6"/>
     </row>
-    <row r="520">
+    <row r="520" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C520" s="6"/>
       <c r="F520" s="6"/>
       <c r="I520" s="6"/>
       <c r="K520" s="6"/>
     </row>
-    <row r="521">
+    <row r="521" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C521" s="6"/>
       <c r="F521" s="6"/>
       <c r="I521" s="6"/>
       <c r="K521" s="6"/>
     </row>
-    <row r="522">
+    <row r="522" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C522" s="6"/>
       <c r="F522" s="6"/>
       <c r="I522" s="6"/>
       <c r="K522" s="6"/>
     </row>
-    <row r="523">
+    <row r="523" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C523" s="6"/>
       <c r="F523" s="6"/>
       <c r="I523" s="6"/>
       <c r="K523" s="6"/>
     </row>
-    <row r="524">
+    <row r="524" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C524" s="6"/>
       <c r="F524" s="6"/>
       <c r="I524" s="6"/>
       <c r="K524" s="6"/>
     </row>
-    <row r="525">
+    <row r="525" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C525" s="6"/>
       <c r="F525" s="6"/>
       <c r="I525" s="6"/>
       <c r="K525" s="6"/>
     </row>
-    <row r="526">
+    <row r="526" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C526" s="6"/>
       <c r="F526" s="6"/>
       <c r="I526" s="6"/>
       <c r="K526" s="6"/>
     </row>
-    <row r="527">
+    <row r="527" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C527" s="6"/>
       <c r="F527" s="6"/>
       <c r="I527" s="6"/>
       <c r="K527" s="6"/>
     </row>
-    <row r="528">
+    <row r="528" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C528" s="6"/>
       <c r="F528" s="6"/>
       <c r="I528" s="6"/>
       <c r="K528" s="6"/>
     </row>
-    <row r="529">
+    <row r="529" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C529" s="6"/>
       <c r="F529" s="6"/>
       <c r="I529" s="6"/>
       <c r="K529" s="6"/>
     </row>
-    <row r="530">
+    <row r="530" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C530" s="6"/>
       <c r="F530" s="6"/>
       <c r="I530" s="6"/>
       <c r="K530" s="6"/>
     </row>
-    <row r="531">
+    <row r="531" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C531" s="6"/>
       <c r="F531" s="6"/>
       <c r="I531" s="6"/>
       <c r="K531" s="6"/>
     </row>
-    <row r="532">
+    <row r="532" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C532" s="6"/>
       <c r="F532" s="6"/>
       <c r="I532" s="6"/>
       <c r="K532" s="6"/>
     </row>
-    <row r="533">
+    <row r="533" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C533" s="6"/>
       <c r="F533" s="6"/>
       <c r="I533" s="6"/>
       <c r="K533" s="6"/>
     </row>
-    <row r="534">
+    <row r="534" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C534" s="6"/>
       <c r="F534" s="6"/>
       <c r="I534" s="6"/>
       <c r="K534" s="6"/>
     </row>
-    <row r="535">
+    <row r="535" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C535" s="6"/>
       <c r="F535" s="6"/>
       <c r="I535" s="6"/>
       <c r="K535" s="6"/>
     </row>
-    <row r="536">
+    <row r="536" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C536" s="6"/>
       <c r="F536" s="6"/>
       <c r="I536" s="6"/>
       <c r="K536" s="6"/>
     </row>
-    <row r="537">
+    <row r="537" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C537" s="6"/>
       <c r="F537" s="6"/>
       <c r="I537" s="6"/>
       <c r="K537" s="6"/>
     </row>
-    <row r="538">
+    <row r="538" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C538" s="6"/>
       <c r="F538" s="6"/>
       <c r="I538" s="6"/>
       <c r="K538" s="6"/>
     </row>
-    <row r="539">
+    <row r="539" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C539" s="6"/>
       <c r="F539" s="6"/>
       <c r="I539" s="6"/>
       <c r="K539" s="6"/>
     </row>
-    <row r="540">
+    <row r="540" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C540" s="6"/>
       <c r="F540" s="6"/>
       <c r="I540" s="6"/>
       <c r="K540" s="6"/>
     </row>
-    <row r="541">
+    <row r="541" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C541" s="6"/>
       <c r="F541" s="6"/>
       <c r="I541" s="6"/>
       <c r="K541" s="6"/>
     </row>
-    <row r="542">
+    <row r="542" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C542" s="6"/>
       <c r="F542" s="6"/>
       <c r="I542" s="6"/>
       <c r="K542" s="6"/>
     </row>
-    <row r="543">
+    <row r="543" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C543" s="6"/>
       <c r="F543" s="6"/>
       <c r="I543" s="6"/>
       <c r="K543" s="6"/>
     </row>
-    <row r="544">
+    <row r="544" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C544" s="6"/>
       <c r="F544" s="6"/>
       <c r="I544" s="6"/>
       <c r="K544" s="6"/>
     </row>
-    <row r="545">
+    <row r="545" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C545" s="6"/>
       <c r="F545" s="6"/>
       <c r="I545" s="6"/>
       <c r="K545" s="6"/>
     </row>
-    <row r="546">
+    <row r="546" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C546" s="6"/>
       <c r="F546" s="6"/>
       <c r="I546" s="6"/>
       <c r="K546" s="6"/>
     </row>
-    <row r="547">
+    <row r="547" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C547" s="6"/>
       <c r="F547" s="6"/>
       <c r="I547" s="6"/>
       <c r="K547" s="6"/>
     </row>
-    <row r="548">
+    <row r="548" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C548" s="6"/>
       <c r="F548" s="6"/>
       <c r="I548" s="6"/>
       <c r="K548" s="6"/>
     </row>
-    <row r="549">
+    <row r="549" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C549" s="6"/>
       <c r="F549" s="6"/>
       <c r="I549" s="6"/>
       <c r="K549" s="6"/>
     </row>
-    <row r="550">
+    <row r="550" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C550" s="6"/>
       <c r="F550" s="6"/>
       <c r="I550" s="6"/>
       <c r="K550" s="6"/>
     </row>
-    <row r="551">
+    <row r="551" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C551" s="6"/>
       <c r="F551" s="6"/>
       <c r="I551" s="6"/>
       <c r="K551" s="6"/>
     </row>
-    <row r="552">
+    <row r="552" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C552" s="6"/>
       <c r="F552" s="6"/>
       <c r="I552" s="6"/>
       <c r="K552" s="6"/>
     </row>
-    <row r="553">
+    <row r="553" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C553" s="6"/>
       <c r="F553" s="6"/>
       <c r="I553" s="6"/>
       <c r="K553" s="6"/>
     </row>
-    <row r="554">
+    <row r="554" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C554" s="6"/>
       <c r="F554" s="6"/>
       <c r="I554" s="6"/>
       <c r="K554" s="6"/>
     </row>
-    <row r="555">
+    <row r="555" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C555" s="6"/>
       <c r="F555" s="6"/>
       <c r="I555" s="6"/>
       <c r="K555" s="6"/>
     </row>
-    <row r="556">
+    <row r="556" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C556" s="6"/>
       <c r="F556" s="6"/>
       <c r="I556" s="6"/>
       <c r="K556" s="6"/>
     </row>
-    <row r="557">
+    <row r="557" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C557" s="6"/>
       <c r="F557" s="6"/>
       <c r="I557" s="6"/>
       <c r="K557" s="6"/>
     </row>
-    <row r="558">
+    <row r="558" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C558" s="6"/>
       <c r="F558" s="6"/>
       <c r="I558" s="6"/>
       <c r="K558" s="6"/>
     </row>
-    <row r="559">
+    <row r="559" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C559" s="6"/>
       <c r="F559" s="6"/>
       <c r="I559" s="6"/>
       <c r="K559" s="6"/>
     </row>
-    <row r="560">
+    <row r="560" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C560" s="6"/>
       <c r="F560" s="6"/>
       <c r="I560" s="6"/>
       <c r="K560" s="6"/>
     </row>
-    <row r="561">
+    <row r="561" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C561" s="6"/>
       <c r="F561" s="6"/>
       <c r="I561" s="6"/>
       <c r="K561" s="6"/>
     </row>
-    <row r="562">
+    <row r="562" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C562" s="6"/>
       <c r="F562" s="6"/>
       <c r="I562" s="6"/>
       <c r="K562" s="6"/>
     </row>
-    <row r="563">
+    <row r="563" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C563" s="6"/>
       <c r="F563" s="6"/>
       <c r="I563" s="6"/>
       <c r="K563" s="6"/>
     </row>
-    <row r="564">
+    <row r="564" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C564" s="6"/>
       <c r="F564" s="6"/>
       <c r="I564" s="6"/>
       <c r="K564" s="6"/>
     </row>
-    <row r="565">
+    <row r="565" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C565" s="6"/>
       <c r="F565" s="6"/>
       <c r="I565" s="6"/>
       <c r="K565" s="6"/>
     </row>
-    <row r="566">
+    <row r="566" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C566" s="6"/>
       <c r="F566" s="6"/>
       <c r="I566" s="6"/>
       <c r="K566" s="6"/>
     </row>
-    <row r="567">
+    <row r="567" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C567" s="6"/>
       <c r="F567" s="6"/>
       <c r="I567" s="6"/>
       <c r="K567" s="6"/>
     </row>
-    <row r="568">
+    <row r="568" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C568" s="6"/>
       <c r="F568" s="6"/>
       <c r="I568" s="6"/>
       <c r="K568" s="6"/>
     </row>
-    <row r="569">
+    <row r="569" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C569" s="6"/>
       <c r="F569" s="6"/>
       <c r="I569" s="6"/>
       <c r="K569" s="6"/>
     </row>
-    <row r="570">
+    <row r="570" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C570" s="6"/>
       <c r="F570" s="6"/>
       <c r="I570" s="6"/>
       <c r="K570" s="6"/>
     </row>
-    <row r="571">
+    <row r="571" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C571" s="6"/>
       <c r="F571" s="6"/>
       <c r="I571" s="6"/>
       <c r="K571" s="6"/>
     </row>
-    <row r="572">
+    <row r="572" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C572" s="6"/>
       <c r="F572" s="6"/>
       <c r="I572" s="6"/>
       <c r="K572" s="6"/>
     </row>
-    <row r="573">
+    <row r="573" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C573" s="6"/>
       <c r="F573" s="6"/>
       <c r="I573" s="6"/>
       <c r="K573" s="6"/>
     </row>
-    <row r="574">
+    <row r="574" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C574" s="6"/>
       <c r="F574" s="6"/>
       <c r="I574" s="6"/>
       <c r="K574" s="6"/>
     </row>
-    <row r="575">
+    <row r="575" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C575" s="6"/>
       <c r="F575" s="6"/>
       <c r="I575" s="6"/>
       <c r="K575" s="6"/>
     </row>
-    <row r="576">
+    <row r="576" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C576" s="6"/>
       <c r="F576" s="6"/>
       <c r="I576" s="6"/>
       <c r="K576" s="6"/>
     </row>
-    <row r="577">
+    <row r="577" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C577" s="6"/>
       <c r="F577" s="6"/>
       <c r="I577" s="6"/>
       <c r="K577" s="6"/>
     </row>
-    <row r="578">
+    <row r="578" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C578" s="6"/>
       <c r="F578" s="6"/>
       <c r="I578" s="6"/>
       <c r="K578" s="6"/>
     </row>
-    <row r="579">
+    <row r="579" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C579" s="6"/>
       <c r="F579" s="6"/>
       <c r="I579" s="6"/>
       <c r="K579" s="6"/>
     </row>
-    <row r="580">
+    <row r="580" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C580" s="6"/>
       <c r="F580" s="6"/>
       <c r="I580" s="6"/>
       <c r="K580" s="6"/>
     </row>
-    <row r="581">
+    <row r="581" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C581" s="6"/>
       <c r="F581" s="6"/>
       <c r="I581" s="6"/>
       <c r="K581" s="6"/>
     </row>
-    <row r="582">
+    <row r="582" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C582" s="6"/>
       <c r="F582" s="6"/>
       <c r="I582" s="6"/>
       <c r="K582" s="6"/>
     </row>
-    <row r="583">
+    <row r="583" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C583" s="6"/>
       <c r="F583" s="6"/>
       <c r="I583" s="6"/>
       <c r="K583" s="6"/>
     </row>
-    <row r="584">
+    <row r="584" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C584" s="6"/>
       <c r="F584" s="6"/>
       <c r="I584" s="6"/>
       <c r="K584" s="6"/>
     </row>
-    <row r="585">
+    <row r="585" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C585" s="6"/>
       <c r="F585" s="6"/>
       <c r="I585" s="6"/>
       <c r="K585" s="6"/>
     </row>
-    <row r="586">
+    <row r="586" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C586" s="6"/>
       <c r="F586" s="6"/>
       <c r="I586" s="6"/>
       <c r="K586" s="6"/>
     </row>
-    <row r="587">
+    <row r="587" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C587" s="6"/>
       <c r="F587" s="6"/>
       <c r="I587" s="6"/>
       <c r="K587" s="6"/>
     </row>
-    <row r="588">
+    <row r="588" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C588" s="6"/>
       <c r="F588" s="6"/>
       <c r="I588" s="6"/>
       <c r="K588" s="6"/>
     </row>
-    <row r="589">
+    <row r="589" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C589" s="6"/>
       <c r="F589" s="6"/>
       <c r="I589" s="6"/>
       <c r="K589" s="6"/>
     </row>
-    <row r="590">
+    <row r="590" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C590" s="6"/>
       <c r="F590" s="6"/>
       <c r="I590" s="6"/>
       <c r="K590" s="6"/>
     </row>
-    <row r="591">
+    <row r="591" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C591" s="6"/>
       <c r="F591" s="6"/>
       <c r="I591" s="6"/>
       <c r="K591" s="6"/>
     </row>
-    <row r="592">
+    <row r="592" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C592" s="6"/>
       <c r="F592" s="6"/>
       <c r="I592" s="6"/>
       <c r="K592" s="6"/>
     </row>
-    <row r="593">
+    <row r="593" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C593" s="6"/>
       <c r="F593" s="6"/>
       <c r="I593" s="6"/>
       <c r="K593" s="6"/>
     </row>
-    <row r="594">
+    <row r="594" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C594" s="6"/>
       <c r="F594" s="6"/>
       <c r="I594" s="6"/>
       <c r="K594" s="6"/>
     </row>
-    <row r="595">
+    <row r="595" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C595" s="6"/>
       <c r="F595" s="6"/>
       <c r="I595" s="6"/>
       <c r="K595" s="6"/>
     </row>
-    <row r="596">
+    <row r="596" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C596" s="6"/>
       <c r="F596" s="6"/>
       <c r="I596" s="6"/>
       <c r="K596" s="6"/>
     </row>
-    <row r="597">
+    <row r="597" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C597" s="6"/>
       <c r="F597" s="6"/>
       <c r="I597" s="6"/>
       <c r="K597" s="6"/>
     </row>
-    <row r="598">
+    <row r="598" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C598" s="6"/>
       <c r="F598" s="6"/>
       <c r="I598" s="6"/>
       <c r="K598" s="6"/>
     </row>
-    <row r="599">
+    <row r="599" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C599" s="6"/>
       <c r="F599" s="6"/>
       <c r="I599" s="6"/>
       <c r="K599" s="6"/>
     </row>
-    <row r="600">
+    <row r="600" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C600" s="6"/>
       <c r="F600" s="6"/>
       <c r="I600" s="6"/>
       <c r="K600" s="6"/>
     </row>
-    <row r="601">
+    <row r="601" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C601" s="6"/>
       <c r="F601" s="6"/>
       <c r="I601" s="6"/>
       <c r="K601" s="6"/>
     </row>
-    <row r="602">
+    <row r="602" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C602" s="6"/>
       <c r="F602" s="6"/>
       <c r="I602" s="6"/>
       <c r="K602" s="6"/>
     </row>
-    <row r="603">
+    <row r="603" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C603" s="6"/>
       <c r="F603" s="6"/>
       <c r="I603" s="6"/>
       <c r="K603" s="6"/>
     </row>
-    <row r="604">
+    <row r="604" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C604" s="6"/>
       <c r="F604" s="6"/>
       <c r="I604" s="6"/>
       <c r="K604" s="6"/>
     </row>
-    <row r="605">
+    <row r="605" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C605" s="6"/>
       <c r="F605" s="6"/>
       <c r="I605" s="6"/>
       <c r="K605" s="6"/>
     </row>
-    <row r="606">
+    <row r="606" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C606" s="6"/>
       <c r="F606" s="6"/>
       <c r="I606" s="6"/>
       <c r="K606" s="6"/>
     </row>
-    <row r="607">
+    <row r="607" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C607" s="6"/>
       <c r="F607" s="6"/>
       <c r="I607" s="6"/>
       <c r="K607" s="6"/>
     </row>
-    <row r="608">
+    <row r="608" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C608" s="6"/>
       <c r="F608" s="6"/>
       <c r="I608" s="6"/>
       <c r="K608" s="6"/>
     </row>
-    <row r="609">
+    <row r="609" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C609" s="6"/>
       <c r="F609" s="6"/>
       <c r="I609" s="6"/>
       <c r="K609" s="6"/>
     </row>
-    <row r="610">
+    <row r="610" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C610" s="6"/>
       <c r="F610" s="6"/>
       <c r="I610" s="6"/>
       <c r="K610" s="6"/>
     </row>
-    <row r="611">
+    <row r="611" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C611" s="6"/>
       <c r="F611" s="6"/>
       <c r="I611" s="6"/>
       <c r="K611" s="6"/>
     </row>
-    <row r="612">
+    <row r="612" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C612" s="6"/>
       <c r="F612" s="6"/>
       <c r="I612" s="6"/>
       <c r="K612" s="6"/>
     </row>
-    <row r="613">
+    <row r="613" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C613" s="6"/>
       <c r="F613" s="6"/>
       <c r="I613" s="6"/>
       <c r="K613" s="6"/>
     </row>
-    <row r="614">
+    <row r="614" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C614" s="6"/>
       <c r="F614" s="6"/>
       <c r="I614" s="6"/>
       <c r="K614" s="6"/>
     </row>
-    <row r="615">
+    <row r="615" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C615" s="6"/>
       <c r="F615" s="6"/>
       <c r="I615" s="6"/>
       <c r="K615" s="6"/>
     </row>
-    <row r="616">
+    <row r="616" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C616" s="6"/>
       <c r="F616" s="6"/>
       <c r="I616" s="6"/>
       <c r="K616" s="6"/>
     </row>
-    <row r="617">
+    <row r="617" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C617" s="6"/>
       <c r="F617" s="6"/>
       <c r="I617" s="6"/>
       <c r="K617" s="6"/>
     </row>
-    <row r="618">
+    <row r="618" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C618" s="6"/>
       <c r="F618" s="6"/>
       <c r="I618" s="6"/>
       <c r="K618" s="6"/>
     </row>
-    <row r="619">
+    <row r="619" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C619" s="6"/>
       <c r="F619" s="6"/>
       <c r="I619" s="6"/>
       <c r="K619" s="6"/>
     </row>
-    <row r="620">
+    <row r="620" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C620" s="6"/>
       <c r="F620" s="6"/>
       <c r="I620" s="6"/>
       <c r="K620" s="6"/>
     </row>
-    <row r="621">
+    <row r="621" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C621" s="6"/>
       <c r="F621" s="6"/>
       <c r="I621" s="6"/>
       <c r="K621" s="6"/>
     </row>
-    <row r="622">
+    <row r="622" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C622" s="6"/>
       <c r="F622" s="6"/>
       <c r="I622" s="6"/>
       <c r="K622" s="6"/>
     </row>
-    <row r="623">
+    <row r="623" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C623" s="6"/>
       <c r="F623" s="6"/>
       <c r="I623" s="6"/>
       <c r="K623" s="6"/>
     </row>
-    <row r="624">
+    <row r="624" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C624" s="6"/>
       <c r="F624" s="6"/>
       <c r="I624" s="6"/>
       <c r="K624" s="6"/>
     </row>
-    <row r="625">
+    <row r="625" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C625" s="6"/>
       <c r="F625" s="6"/>
       <c r="I625" s="6"/>
       <c r="K625" s="6"/>
     </row>
-    <row r="626">
+    <row r="626" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C626" s="6"/>
       <c r="F626" s="6"/>
       <c r="I626" s="6"/>
       <c r="K626" s="6"/>
     </row>
-    <row r="627">
+    <row r="627" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C627" s="6"/>
       <c r="F627" s="6"/>
       <c r="I627" s="6"/>
       <c r="K627" s="6"/>
     </row>
-    <row r="628">
+    <row r="628" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C628" s="6"/>
       <c r="F628" s="6"/>
       <c r="I628" s="6"/>
       <c r="K628" s="6"/>
     </row>
-    <row r="629">
+    <row r="629" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C629" s="6"/>
       <c r="F629" s="6"/>
       <c r="I629" s="6"/>
       <c r="K629" s="6"/>
     </row>
-    <row r="630">
+    <row r="630" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C630" s="6"/>
       <c r="F630" s="6"/>
       <c r="I630" s="6"/>
       <c r="K630" s="6"/>
     </row>
-    <row r="631">
+    <row r="631" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C631" s="6"/>
       <c r="F631" s="6"/>
       <c r="I631" s="6"/>
       <c r="K631" s="6"/>
     </row>
-    <row r="632">
+    <row r="632" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C632" s="6"/>
       <c r="F632" s="6"/>
       <c r="I632" s="6"/>
       <c r="K632" s="6"/>
     </row>
-    <row r="633">
+    <row r="633" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C633" s="6"/>
       <c r="F633" s="6"/>
       <c r="I633" s="6"/>
       <c r="K633" s="6"/>
     </row>
-    <row r="634">
+    <row r="634" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C634" s="6"/>
       <c r="F634" s="6"/>
       <c r="I634" s="6"/>
       <c r="K634" s="6"/>
     </row>
-    <row r="635">
+    <row r="635" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C635" s="6"/>
       <c r="F635" s="6"/>
       <c r="I635" s="6"/>
       <c r="K635" s="6"/>
     </row>
-    <row r="636">
+    <row r="636" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C636" s="6"/>
       <c r="F636" s="6"/>
       <c r="I636" s="6"/>
       <c r="K636" s="6"/>
     </row>
-    <row r="637">
+    <row r="637" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C637" s="6"/>
       <c r="F637" s="6"/>
       <c r="I637" s="6"/>
       <c r="K637" s="6"/>
     </row>
-    <row r="638">
+    <row r="638" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C638" s="6"/>
       <c r="F638" s="6"/>
       <c r="I638" s="6"/>
       <c r="K638" s="6"/>
     </row>
-    <row r="639">
+    <row r="639" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C639" s="6"/>
       <c r="F639" s="6"/>
       <c r="I639" s="6"/>
       <c r="K639" s="6"/>
     </row>
-    <row r="640">
+    <row r="640" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C640" s="6"/>
       <c r="F640" s="6"/>
       <c r="I640" s="6"/>
       <c r="K640" s="6"/>
     </row>
-    <row r="641">
+    <row r="641" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C641" s="6"/>
       <c r="F641" s="6"/>
       <c r="I641" s="6"/>
       <c r="K641" s="6"/>
     </row>
-    <row r="642">
+    <row r="642" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C642" s="6"/>
       <c r="F642" s="6"/>
       <c r="I642" s="6"/>
       <c r="K642" s="6"/>
     </row>
-    <row r="643">
+    <row r="643" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C643" s="6"/>
       <c r="F643" s="6"/>
       <c r="I643" s="6"/>
       <c r="K643" s="6"/>
     </row>
-    <row r="644">
+    <row r="644" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C644" s="6"/>
       <c r="F644" s="6"/>
       <c r="I644" s="6"/>
       <c r="K644" s="6"/>
     </row>
-    <row r="645">
+    <row r="645" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C645" s="6"/>
       <c r="F645" s="6"/>
       <c r="I645" s="6"/>
       <c r="K645" s="6"/>
     </row>
-    <row r="646">
+    <row r="646" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C646" s="6"/>
       <c r="F646" s="6"/>
       <c r="I646" s="6"/>
       <c r="K646" s="6"/>
     </row>
-    <row r="647">
+    <row r="647" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C647" s="6"/>
       <c r="F647" s="6"/>
       <c r="I647" s="6"/>
       <c r="K647" s="6"/>
     </row>
-    <row r="648">
+    <row r="648" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C648" s="6"/>
       <c r="F648" s="6"/>
       <c r="I648" s="6"/>
       <c r="K648" s="6"/>
     </row>
-    <row r="649">
+    <row r="649" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C649" s="6"/>
       <c r="F649" s="6"/>
       <c r="I649" s="6"/>
       <c r="K649" s="6"/>
     </row>
-    <row r="650">
+    <row r="650" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C650" s="6"/>
       <c r="F650" s="6"/>
       <c r="I650" s="6"/>
       <c r="K650" s="6"/>
     </row>
-    <row r="651">
+    <row r="651" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C651" s="6"/>
       <c r="F651" s="6"/>
       <c r="I651" s="6"/>
       <c r="K651" s="6"/>
     </row>
-    <row r="652">
+    <row r="652" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C652" s="6"/>
       <c r="F652" s="6"/>
       <c r="I652" s="6"/>
       <c r="K652" s="6"/>
     </row>
-    <row r="653">
+    <row r="653" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C653" s="6"/>
       <c r="F653" s="6"/>
       <c r="I653" s="6"/>
       <c r="K653" s="6"/>
     </row>
-    <row r="654">
+    <row r="654" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C654" s="6"/>
       <c r="F654" s="6"/>
       <c r="I654" s="6"/>
       <c r="K654" s="6"/>
     </row>
-    <row r="655">
+    <row r="655" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C655" s="6"/>
       <c r="F655" s="6"/>
       <c r="I655" s="6"/>
       <c r="K655" s="6"/>
     </row>
-    <row r="656">
+    <row r="656" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C656" s="6"/>
       <c r="F656" s="6"/>
       <c r="I656" s="6"/>
       <c r="K656" s="6"/>
     </row>
-    <row r="657">
+    <row r="657" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C657" s="6"/>
       <c r="F657" s="6"/>
       <c r="I657" s="6"/>
       <c r="K657" s="6"/>
     </row>
-    <row r="658">
+    <row r="658" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C658" s="6"/>
       <c r="F658" s="6"/>
       <c r="I658" s="6"/>
       <c r="K658" s="6"/>
     </row>
-    <row r="659">
+    <row r="659" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C659" s="6"/>
       <c r="F659" s="6"/>
       <c r="I659" s="6"/>
       <c r="K659" s="6"/>
     </row>
-    <row r="660">
+    <row r="660" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C660" s="6"/>
       <c r="F660" s="6"/>
       <c r="I660" s="6"/>
       <c r="K660" s="6"/>
     </row>
-    <row r="661">
+    <row r="661" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C661" s="6"/>
       <c r="F661" s="6"/>
       <c r="I661" s="6"/>
       <c r="K661" s="6"/>
     </row>
-    <row r="662">
+    <row r="662" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C662" s="6"/>
       <c r="F662" s="6"/>
       <c r="I662" s="6"/>
       <c r="K662" s="6"/>
     </row>
-    <row r="663">
+    <row r="663" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C663" s="6"/>
       <c r="F663" s="6"/>
       <c r="I663" s="6"/>
       <c r="K663" s="6"/>
     </row>
-    <row r="664">
+    <row r="664" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C664" s="6"/>
       <c r="F664" s="6"/>
       <c r="I664" s="6"/>
       <c r="K664" s="6"/>
     </row>
-    <row r="665">
+    <row r="665" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C665" s="6"/>
       <c r="F665" s="6"/>
       <c r="I665" s="6"/>
       <c r="K665" s="6"/>
     </row>
-    <row r="666">
+    <row r="666" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C666" s="6"/>
       <c r="F666" s="6"/>
       <c r="I666" s="6"/>
       <c r="K666" s="6"/>
     </row>
-    <row r="667">
+    <row r="667" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C667" s="6"/>
       <c r="F667" s="6"/>
       <c r="I667" s="6"/>
       <c r="K667" s="6"/>
     </row>
-    <row r="668">
+    <row r="668" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C668" s="6"/>
       <c r="F668" s="6"/>
       <c r="I668" s="6"/>
       <c r="K668" s="6"/>
     </row>
-    <row r="669">
+    <row r="669" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C669" s="6"/>
       <c r="F669" s="6"/>
       <c r="I669" s="6"/>
       <c r="K669" s="6"/>
     </row>
-    <row r="670">
+    <row r="670" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C670" s="6"/>
       <c r="F670" s="6"/>
       <c r="I670" s="6"/>
       <c r="K670" s="6"/>
     </row>
-    <row r="671">
+    <row r="671" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C671" s="6"/>
       <c r="F671" s="6"/>
       <c r="I671" s="6"/>
       <c r="K671" s="6"/>
     </row>
-    <row r="672">
+    <row r="672" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C672" s="6"/>
       <c r="F672" s="6"/>
       <c r="I672" s="6"/>
       <c r="K672" s="6"/>
     </row>
-    <row r="673">
+    <row r="673" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C673" s="6"/>
       <c r="F673" s="6"/>
       <c r="I673" s="6"/>
       <c r="K673" s="6"/>
     </row>
-    <row r="674">
+    <row r="674" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C674" s="6"/>
       <c r="F674" s="6"/>
       <c r="I674" s="6"/>
       <c r="K674" s="6"/>
     </row>
-    <row r="675">
+    <row r="675" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C675" s="6"/>
       <c r="F675" s="6"/>
       <c r="I675" s="6"/>
       <c r="K675" s="6"/>
     </row>
-    <row r="676">
+    <row r="676" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C676" s="6"/>
       <c r="F676" s="6"/>
       <c r="I676" s="6"/>
       <c r="K676" s="6"/>
     </row>
-    <row r="677">
+    <row r="677" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C677" s="6"/>
       <c r="F677" s="6"/>
       <c r="I677" s="6"/>
       <c r="K677" s="6"/>
     </row>
-    <row r="678">
+    <row r="678" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C678" s="6"/>
       <c r="F678" s="6"/>
       <c r="I678" s="6"/>
       <c r="K678" s="6"/>
     </row>
-    <row r="679">
+    <row r="679" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C679" s="6"/>
       <c r="F679" s="6"/>
       <c r="I679" s="6"/>
       <c r="K679" s="6"/>
     </row>
-    <row r="680">
+    <row r="680" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C680" s="6"/>
       <c r="F680" s="6"/>
       <c r="I680" s="6"/>
       <c r="K680" s="6"/>
     </row>
-    <row r="681">
+    <row r="681" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C681" s="6"/>
       <c r="F681" s="6"/>
       <c r="I681" s="6"/>
       <c r="K681" s="6"/>
     </row>
-    <row r="682">
+    <row r="682" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C682" s="6"/>
       <c r="F682" s="6"/>
       <c r="I682" s="6"/>
       <c r="K682" s="6"/>
     </row>
-    <row r="683">
+    <row r="683" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C683" s="6"/>
       <c r="F683" s="6"/>
       <c r="I683" s="6"/>
       <c r="K683" s="6"/>
     </row>
-    <row r="684">
+    <row r="684" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C684" s="6"/>
       <c r="F684" s="6"/>
       <c r="I684" s="6"/>
       <c r="K684" s="6"/>
     </row>
-    <row r="685">
+    <row r="685" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C685" s="6"/>
       <c r="F685" s="6"/>
       <c r="I685" s="6"/>
       <c r="K685" s="6"/>
     </row>
-    <row r="686">
+    <row r="686" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C686" s="6"/>
       <c r="F686" s="6"/>
       <c r="I686" s="6"/>
       <c r="K686" s="6"/>
     </row>
-    <row r="687">
+    <row r="687" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C687" s="6"/>
       <c r="F687" s="6"/>
       <c r="I687" s="6"/>
       <c r="K687" s="6"/>
     </row>
-    <row r="688">
+    <row r="688" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C688" s="6"/>
       <c r="F688" s="6"/>
       <c r="I688" s="6"/>
       <c r="K688" s="6"/>
     </row>
-    <row r="689">
+    <row r="689" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C689" s="6"/>
       <c r="F689" s="6"/>
       <c r="I689" s="6"/>
       <c r="K689" s="6"/>
     </row>
-    <row r="690">
+    <row r="690" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C690" s="6"/>
       <c r="F690" s="6"/>
       <c r="I690" s="6"/>
       <c r="K690" s="6"/>
     </row>
-    <row r="691">
+    <row r="691" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C691" s="6"/>
       <c r="F691" s="6"/>
       <c r="I691" s="6"/>
       <c r="K691" s="6"/>
     </row>
-    <row r="692">
+    <row r="692" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C692" s="6"/>
       <c r="F692" s="6"/>
       <c r="I692" s="6"/>
       <c r="K692" s="6"/>
     </row>
-    <row r="693">
+    <row r="693" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C693" s="6"/>
       <c r="F693" s="6"/>
       <c r="I693" s="6"/>
       <c r="K693" s="6"/>
     </row>
-    <row r="694">
+    <row r="694" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C694" s="6"/>
       <c r="F694" s="6"/>
       <c r="I694" s="6"/>
       <c r="K694" s="6"/>
     </row>
-    <row r="695">
+    <row r="695" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C695" s="6"/>
       <c r="F695" s="6"/>
       <c r="I695" s="6"/>
       <c r="K695" s="6"/>
     </row>
-    <row r="696">
+    <row r="696" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C696" s="6"/>
       <c r="F696" s="6"/>
       <c r="I696" s="6"/>
       <c r="K696" s="6"/>
     </row>
-    <row r="697">
+    <row r="697" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C697" s="6"/>
       <c r="F697" s="6"/>
       <c r="I697" s="6"/>
       <c r="K697" s="6"/>
     </row>
-    <row r="698">
+    <row r="698" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C698" s="6"/>
       <c r="F698" s="6"/>
       <c r="I698" s="6"/>
       <c r="K698" s="6"/>
     </row>
-    <row r="699">
+    <row r="699" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C699" s="6"/>
       <c r="F699" s="6"/>
       <c r="I699" s="6"/>
       <c r="K699" s="6"/>
     </row>
-    <row r="700">
+    <row r="700" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C700" s="6"/>
       <c r="F700" s="6"/>
       <c r="I700" s="6"/>
       <c r="K700" s="6"/>
     </row>
-    <row r="701">
+    <row r="701" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C701" s="6"/>
       <c r="F701" s="6"/>
       <c r="I701" s="6"/>
       <c r="K701" s="6"/>
     </row>
-    <row r="702">
+    <row r="702" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C702" s="6"/>
       <c r="F702" s="6"/>
       <c r="I702" s="6"/>
       <c r="K702" s="6"/>
     </row>
-    <row r="703">
+    <row r="703" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C703" s="6"/>
       <c r="F703" s="6"/>
       <c r="I703" s="6"/>
       <c r="K703" s="6"/>
     </row>
-    <row r="704">
+    <row r="704" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C704" s="6"/>
       <c r="F704" s="6"/>
       <c r="I704" s="6"/>
       <c r="K704" s="6"/>
     </row>
-    <row r="705">
+    <row r="705" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C705" s="6"/>
       <c r="F705" s="6"/>
       <c r="I705" s="6"/>
       <c r="K705" s="6"/>
     </row>
-    <row r="706">
+    <row r="706" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C706" s="6"/>
       <c r="F706" s="6"/>
       <c r="I706" s="6"/>
       <c r="K706" s="6"/>
     </row>
-    <row r="707">
+    <row r="707" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C707" s="6"/>
       <c r="F707" s="6"/>
       <c r="I707" s="6"/>
       <c r="K707" s="6"/>
     </row>
-    <row r="708">
+    <row r="708" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C708" s="6"/>
       <c r="F708" s="6"/>
       <c r="I708" s="6"/>
       <c r="K708" s="6"/>
     </row>
-    <row r="709">
+    <row r="709" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C709" s="6"/>
       <c r="F709" s="6"/>
       <c r="I709" s="6"/>
       <c r="K709" s="6"/>
     </row>
-    <row r="710">
+    <row r="710" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C710" s="6"/>
       <c r="F710" s="6"/>
       <c r="I710" s="6"/>
       <c r="K710" s="6"/>
     </row>
-    <row r="711">
+    <row r="711" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C711" s="6"/>
       <c r="F711" s="6"/>
       <c r="I711" s="6"/>
       <c r="K711" s="6"/>
     </row>
-    <row r="712">
+    <row r="712" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C712" s="6"/>
       <c r="F712" s="6"/>
       <c r="I712" s="6"/>
       <c r="K712" s="6"/>
     </row>
-    <row r="713">
+    <row r="713" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C713" s="6"/>
       <c r="F713" s="6"/>
       <c r="I713" s="6"/>
       <c r="K713" s="6"/>
     </row>
-    <row r="714">
+    <row r="714" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C714" s="6"/>
       <c r="F714" s="6"/>
       <c r="I714" s="6"/>
       <c r="K714" s="6"/>
     </row>
-    <row r="715">
+    <row r="715" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C715" s="6"/>
       <c r="F715" s="6"/>
       <c r="I715" s="6"/>
       <c r="K715" s="6"/>
     </row>
-    <row r="716">
+    <row r="716" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C716" s="6"/>
       <c r="F716" s="6"/>
       <c r="I716" s="6"/>
       <c r="K716" s="6"/>
     </row>
-    <row r="717">
+    <row r="717" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C717" s="6"/>
       <c r="F717" s="6"/>
       <c r="I717" s="6"/>
       <c r="K717" s="6"/>
     </row>
-    <row r="718">
+    <row r="718" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C718" s="6"/>
       <c r="F718" s="6"/>
       <c r="I718" s="6"/>
       <c r="K718" s="6"/>
     </row>
-    <row r="719">
+    <row r="719" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C719" s="6"/>
       <c r="F719" s="6"/>
       <c r="I719" s="6"/>
       <c r="K719" s="6"/>
     </row>
-    <row r="720">
+    <row r="720" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C720" s="6"/>
       <c r="F720" s="6"/>
       <c r="I720" s="6"/>
       <c r="K720" s="6"/>
     </row>
-    <row r="721">
+    <row r="721" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C721" s="6"/>
       <c r="F721" s="6"/>
       <c r="I721" s="6"/>
       <c r="K721" s="6"/>
     </row>
-    <row r="722">
+    <row r="722" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C722" s="6"/>
       <c r="F722" s="6"/>
       <c r="I722" s="6"/>
       <c r="K722" s="6"/>
     </row>
-    <row r="723">
+    <row r="723" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C723" s="6"/>
       <c r="F723" s="6"/>
       <c r="I723" s="6"/>
       <c r="K723" s="6"/>
     </row>
-    <row r="724">
+    <row r="724" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C724" s="6"/>
       <c r="F724" s="6"/>
       <c r="I724" s="6"/>
       <c r="K724" s="6"/>
     </row>
-    <row r="725">
+    <row r="725" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C725" s="6"/>
       <c r="F725" s="6"/>
       <c r="I725" s="6"/>
       <c r="K725" s="6"/>
     </row>
-    <row r="726">
+    <row r="726" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C726" s="6"/>
       <c r="F726" s="6"/>
       <c r="I726" s="6"/>
       <c r="K726" s="6"/>
     </row>
-    <row r="727">
+    <row r="727" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C727" s="6"/>
       <c r="F727" s="6"/>
       <c r="I727" s="6"/>
       <c r="K727" s="6"/>
     </row>
-    <row r="728">
+    <row r="728" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C728" s="6"/>
       <c r="F728" s="6"/>
       <c r="I728" s="6"/>
       <c r="K728" s="6"/>
     </row>
-    <row r="729">
+    <row r="729" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C729" s="6"/>
       <c r="F729" s="6"/>
       <c r="I729" s="6"/>
       <c r="K729" s="6"/>
     </row>
-    <row r="730">
+    <row r="730" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C730" s="6"/>
       <c r="F730" s="6"/>
       <c r="I730" s="6"/>
       <c r="K730" s="6"/>
     </row>
-    <row r="731">
+    <row r="731" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C731" s="6"/>
       <c r="F731" s="6"/>
       <c r="I731" s="6"/>
       <c r="K731" s="6"/>
     </row>
-    <row r="732">
+    <row r="732" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C732" s="6"/>
       <c r="F732" s="6"/>
       <c r="I732" s="6"/>
       <c r="K732" s="6"/>
     </row>
-    <row r="733">
+    <row r="733" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C733" s="6"/>
       <c r="F733" s="6"/>
       <c r="I733" s="6"/>
       <c r="K733" s="6"/>
     </row>
-    <row r="734">
+    <row r="734" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C734" s="6"/>
       <c r="F734" s="6"/>
       <c r="I734" s="6"/>
       <c r="K734" s="6"/>
     </row>
-    <row r="735">
+    <row r="735" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C735" s="6"/>
       <c r="F735" s="6"/>
       <c r="I735" s="6"/>
       <c r="K735" s="6"/>
     </row>
-    <row r="736">
+    <row r="736" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C736" s="6"/>
       <c r="F736" s="6"/>
       <c r="I736" s="6"/>
       <c r="K736" s="6"/>
     </row>
-    <row r="737">
+    <row r="737" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C737" s="6"/>
       <c r="F737" s="6"/>
       <c r="I737" s="6"/>
       <c r="K737" s="6"/>
     </row>
-    <row r="738">
+    <row r="738" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C738" s="6"/>
       <c r="F738" s="6"/>
       <c r="I738" s="6"/>
       <c r="K738" s="6"/>
     </row>
-    <row r="739">
+    <row r="739" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C739" s="6"/>
       <c r="F739" s="6"/>
       <c r="I739" s="6"/>
       <c r="K739" s="6"/>
     </row>
-    <row r="740">
+    <row r="740" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C740" s="6"/>
       <c r="F740" s="6"/>
       <c r="I740" s="6"/>
       <c r="K740" s="6"/>
     </row>
-    <row r="741">
+    <row r="741" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C741" s="6"/>
       <c r="F741" s="6"/>
       <c r="I741" s="6"/>
       <c r="K741" s="6"/>
     </row>
-    <row r="742">
+    <row r="742" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C742" s="6"/>
       <c r="F742" s="6"/>
       <c r="I742" s="6"/>
       <c r="K742" s="6"/>
     </row>
-    <row r="743">
+    <row r="743" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C743" s="6"/>
       <c r="F743" s="6"/>
       <c r="I743" s="6"/>
       <c r="K743" s="6"/>
     </row>
-    <row r="744">
+    <row r="744" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C744" s="6"/>
       <c r="F744" s="6"/>
       <c r="I744" s="6"/>
       <c r="K744" s="6"/>
     </row>
-    <row r="745">
+    <row r="745" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C745" s="6"/>
       <c r="F745" s="6"/>
       <c r="I745" s="6"/>
       <c r="K745" s="6"/>
     </row>
-    <row r="746">
+    <row r="746" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C746" s="6"/>
       <c r="F746" s="6"/>
       <c r="I746" s="6"/>
       <c r="K746" s="6"/>
     </row>
-    <row r="747">
+    <row r="747" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C747" s="6"/>
       <c r="F747" s="6"/>
       <c r="I747" s="6"/>
       <c r="K747" s="6"/>
     </row>
-    <row r="748">
+    <row r="748" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C748" s="6"/>
       <c r="F748" s="6"/>
       <c r="I748" s="6"/>
       <c r="K748" s="6"/>
     </row>
-    <row r="749">
+    <row r="749" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C749" s="6"/>
       <c r="F749" s="6"/>
       <c r="I749" s="6"/>
       <c r="K749" s="6"/>
     </row>
-    <row r="750">
+    <row r="750" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C750" s="6"/>
       <c r="F750" s="6"/>
       <c r="I750" s="6"/>
       <c r="K750" s="6"/>
     </row>
-    <row r="751">
+    <row r="751" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C751" s="6"/>
       <c r="F751" s="6"/>
       <c r="I751" s="6"/>
       <c r="K751" s="6"/>
     </row>
-    <row r="752">
+    <row r="752" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C752" s="6"/>
       <c r="F752" s="6"/>
       <c r="I752" s="6"/>
       <c r="K752" s="6"/>
     </row>
-    <row r="753">
+    <row r="753" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C753" s="6"/>
       <c r="F753" s="6"/>
       <c r="I753" s="6"/>
       <c r="K753" s="6"/>
     </row>
-    <row r="754">
+    <row r="754" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C754" s="6"/>
       <c r="F754" s="6"/>
       <c r="I754" s="6"/>
       <c r="K754" s="6"/>
     </row>
-    <row r="755">
+    <row r="755" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C755" s="6"/>
       <c r="F755" s="6"/>
       <c r="I755" s="6"/>
       <c r="K755" s="6"/>
     </row>
-    <row r="756">
+    <row r="756" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C756" s="6"/>
       <c r="F756" s="6"/>
       <c r="I756" s="6"/>
       <c r="K756" s="6"/>
     </row>
-    <row r="757">
+    <row r="757" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C757" s="6"/>
       <c r="F757" s="6"/>
       <c r="I757" s="6"/>
       <c r="K757" s="6"/>
     </row>
-    <row r="758">
+    <row r="758" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C758" s="6"/>
       <c r="F758" s="6"/>
       <c r="I758" s="6"/>
       <c r="K758" s="6"/>
     </row>
-    <row r="759">
+    <row r="759" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C759" s="6"/>
       <c r="F759" s="6"/>
       <c r="I759" s="6"/>
       <c r="K759" s="6"/>
     </row>
-    <row r="760">
+    <row r="760" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C760" s="6"/>
       <c r="F760" s="6"/>
       <c r="I760" s="6"/>
       <c r="K760" s="6"/>
     </row>
-    <row r="761">
+    <row r="761" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C761" s="6"/>
       <c r="F761" s="6"/>
       <c r="I761" s="6"/>
       <c r="K761" s="6"/>
     </row>
-    <row r="762">
+    <row r="762" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C762" s="6"/>
       <c r="F762" s="6"/>
       <c r="I762" s="6"/>
       <c r="K762" s="6"/>
     </row>
-    <row r="763">
+    <row r="763" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C763" s="6"/>
       <c r="F763" s="6"/>
       <c r="I763" s="6"/>
       <c r="K763" s="6"/>
     </row>
-    <row r="764">
+    <row r="764" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C764" s="6"/>
       <c r="F764" s="6"/>
       <c r="I764" s="6"/>
       <c r="K764" s="6"/>
     </row>
-    <row r="765">
+    <row r="765" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C765" s="6"/>
       <c r="F765" s="6"/>
       <c r="I765" s="6"/>
       <c r="K765" s="6"/>
     </row>
-    <row r="766">
+    <row r="766" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C766" s="6"/>
       <c r="F766" s="6"/>
       <c r="I766" s="6"/>
       <c r="K766" s="6"/>
     </row>
-    <row r="767">
+    <row r="767" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C767" s="6"/>
       <c r="F767" s="6"/>
       <c r="I767" s="6"/>
       <c r="K767" s="6"/>
     </row>
-    <row r="768">
+    <row r="768" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C768" s="6"/>
       <c r="F768" s="6"/>
       <c r="I768" s="6"/>
       <c r="K768" s="6"/>
     </row>
-    <row r="769">
+    <row r="769" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C769" s="6"/>
       <c r="F769" s="6"/>
       <c r="I769" s="6"/>
       <c r="K769" s="6"/>
     </row>
-    <row r="770">
+    <row r="770" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C770" s="6"/>
       <c r="F770" s="6"/>
       <c r="I770" s="6"/>
       <c r="K770" s="6"/>
     </row>
-    <row r="771">
+    <row r="771" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C771" s="6"/>
       <c r="F771" s="6"/>
       <c r="I771" s="6"/>
       <c r="K771" s="6"/>
     </row>
-    <row r="772">
+    <row r="772" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C772" s="6"/>
       <c r="F772" s="6"/>
       <c r="I772" s="6"/>
       <c r="K772" s="6"/>
     </row>
-    <row r="773">
+    <row r="773" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C773" s="6"/>
       <c r="F773" s="6"/>
       <c r="I773" s="6"/>
       <c r="K773" s="6"/>
     </row>
-    <row r="774">
+    <row r="774" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C774" s="6"/>
       <c r="F774" s="6"/>
       <c r="I774" s="6"/>
       <c r="K774" s="6"/>
     </row>
-    <row r="775">
+    <row r="775" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C775" s="6"/>
       <c r="F775" s="6"/>
       <c r="I775" s="6"/>
       <c r="K775" s="6"/>
     </row>
-    <row r="776">
+    <row r="776" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C776" s="6"/>
       <c r="F776" s="6"/>
       <c r="I776" s="6"/>
       <c r="K776" s="6"/>
     </row>
-    <row r="777">
+    <row r="777" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C777" s="6"/>
       <c r="F777" s="6"/>
       <c r="I777" s="6"/>
       <c r="K777" s="6"/>
     </row>
-    <row r="778">
+    <row r="778" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C778" s="6"/>
       <c r="F778" s="6"/>
       <c r="I778" s="6"/>
       <c r="K778" s="6"/>
     </row>
-    <row r="779">
+    <row r="779" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C779" s="6"/>
       <c r="F779" s="6"/>
       <c r="I779" s="6"/>
       <c r="K779" s="6"/>
     </row>
-    <row r="780">
+    <row r="780" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C780" s="6"/>
       <c r="F780" s="6"/>
       <c r="I780" s="6"/>
       <c r="K780" s="6"/>
     </row>
-    <row r="781">
+    <row r="781" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C781" s="6"/>
       <c r="F781" s="6"/>
       <c r="I781" s="6"/>
       <c r="K781" s="6"/>
     </row>
-    <row r="782">
+    <row r="782" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C782" s="6"/>
       <c r="F782" s="6"/>
       <c r="I782" s="6"/>
       <c r="K782" s="6"/>
     </row>
-    <row r="783">
+    <row r="783" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C783" s="6"/>
       <c r="F783" s="6"/>
       <c r="I783" s="6"/>
       <c r="K783" s="6"/>
     </row>
-    <row r="784">
+    <row r="784" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C784" s="6"/>
       <c r="F784" s="6"/>
       <c r="I784" s="6"/>
       <c r="K784" s="6"/>
     </row>
-    <row r="785">
+    <row r="785" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C785" s="6"/>
       <c r="F785" s="6"/>
       <c r="I785" s="6"/>
       <c r="K785" s="6"/>
     </row>
-    <row r="786">
+    <row r="786" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C786" s="6"/>
       <c r="F786" s="6"/>
       <c r="I786" s="6"/>
       <c r="K786" s="6"/>
     </row>
-    <row r="787">
+    <row r="787" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C787" s="6"/>
       <c r="F787" s="6"/>
       <c r="I787" s="6"/>
       <c r="K787" s="6"/>
     </row>
-    <row r="788">
+    <row r="788" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C788" s="6"/>
       <c r="F788" s="6"/>
       <c r="I788" s="6"/>
       <c r="K788" s="6"/>
     </row>
-    <row r="789">
+    <row r="789" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C789" s="6"/>
       <c r="F789" s="6"/>
       <c r="I789" s="6"/>
       <c r="K789" s="6"/>
     </row>
-    <row r="790">
+    <row r="790" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C790" s="6"/>
       <c r="F790" s="6"/>
       <c r="I790" s="6"/>
       <c r="K790" s="6"/>
     </row>
-    <row r="791">
+    <row r="791" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C791" s="6"/>
       <c r="F791" s="6"/>
       <c r="I791" s="6"/>
       <c r="K791" s="6"/>
     </row>
-    <row r="792">
+    <row r="792" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C792" s="6"/>
       <c r="F792" s="6"/>
       <c r="I792" s="6"/>
       <c r="K792" s="6"/>
     </row>
-    <row r="793">
+    <row r="793" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C793" s="6"/>
       <c r="F793" s="6"/>
       <c r="I793" s="6"/>
       <c r="K793" s="6"/>
     </row>
-    <row r="794">
+    <row r="794" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C794" s="6"/>
       <c r="F794" s="6"/>
       <c r="I794" s="6"/>
       <c r="K794" s="6"/>
     </row>
-    <row r="795">
+    <row r="795" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C795" s="6"/>
       <c r="F795" s="6"/>
       <c r="I795" s="6"/>
       <c r="K795" s="6"/>
     </row>
-    <row r="796">
+    <row r="796" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C796" s="6"/>
       <c r="F796" s="6"/>
       <c r="I796" s="6"/>
       <c r="K796" s="6"/>
     </row>
-    <row r="797">
+    <row r="797" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C797" s="6"/>
       <c r="F797" s="6"/>
       <c r="I797" s="6"/>
       <c r="K797" s="6"/>
     </row>
-    <row r="798">
+    <row r="798" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C798" s="6"/>
       <c r="F798" s="6"/>
       <c r="I798" s="6"/>
       <c r="K798" s="6"/>
     </row>
-    <row r="799">
+    <row r="799" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C799" s="6"/>
       <c r="F799" s="6"/>
       <c r="I799" s="6"/>
       <c r="K799" s="6"/>
     </row>
-    <row r="800">
+    <row r="800" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C800" s="6"/>
       <c r="F800" s="6"/>
       <c r="I800" s="6"/>
       <c r="K800" s="6"/>
     </row>
-    <row r="801">
+    <row r="801" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C801" s="6"/>
       <c r="F801" s="6"/>
       <c r="I801" s="6"/>
       <c r="K801" s="6"/>
     </row>
-    <row r="802">
+    <row r="802" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C802" s="6"/>
       <c r="F802" s="6"/>
       <c r="I802" s="6"/>
       <c r="K802" s="6"/>
     </row>
-    <row r="803">
+    <row r="803" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C803" s="6"/>
       <c r="F803" s="6"/>
       <c r="I803" s="6"/>
       <c r="K803" s="6"/>
     </row>
-    <row r="804">
+    <row r="804" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C804" s="6"/>
       <c r="F804" s="6"/>
       <c r="I804" s="6"/>
       <c r="K804" s="6"/>
     </row>
-    <row r="805">
+    <row r="805" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C805" s="6"/>
       <c r="F805" s="6"/>
       <c r="I805" s="6"/>
       <c r="K805" s="6"/>
     </row>
-    <row r="806">
+    <row r="806" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C806" s="6"/>
       <c r="F806" s="6"/>
       <c r="I806" s="6"/>
       <c r="K806" s="6"/>
     </row>
-    <row r="807">
+    <row r="807" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C807" s="6"/>
       <c r="F807" s="6"/>
       <c r="I807" s="6"/>
       <c r="K807" s="6"/>
     </row>
-    <row r="808">
+    <row r="808" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C808" s="6"/>
       <c r="F808" s="6"/>
       <c r="I808" s="6"/>
       <c r="K808" s="6"/>
     </row>
-    <row r="809">
+    <row r="809" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C809" s="6"/>
       <c r="F809" s="6"/>
       <c r="I809" s="6"/>
       <c r="K809" s="6"/>
     </row>
-    <row r="810">
+    <row r="810" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C810" s="6"/>
       <c r="F810" s="6"/>
       <c r="I810" s="6"/>
       <c r="K810" s="6"/>
     </row>
-    <row r="811">
+    <row r="811" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C811" s="6"/>
       <c r="F811" s="6"/>
       <c r="I811" s="6"/>
       <c r="K811" s="6"/>
     </row>
-    <row r="812">
+    <row r="812" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C812" s="6"/>
       <c r="F812" s="6"/>
       <c r="I812" s="6"/>
       <c r="K812" s="6"/>
     </row>
-    <row r="813">
+    <row r="813" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C813" s="6"/>
       <c r="F813" s="6"/>
       <c r="I813" s="6"/>
       <c r="K813" s="6"/>
     </row>
-    <row r="814">
+    <row r="814" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C814" s="6"/>
       <c r="F814" s="6"/>
       <c r="I814" s="6"/>
       <c r="K814" s="6"/>
     </row>
-    <row r="815">
+    <row r="815" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C815" s="6"/>
       <c r="F815" s="6"/>
       <c r="I815" s="6"/>
       <c r="K815" s="6"/>
     </row>
-    <row r="816">
+    <row r="816" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C816" s="6"/>
       <c r="F816" s="6"/>
       <c r="I816" s="6"/>
       <c r="K816" s="6"/>
     </row>
-    <row r="817">
+    <row r="817" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C817" s="6"/>
       <c r="F817" s="6"/>
       <c r="I817" s="6"/>
       <c r="K817" s="6"/>
     </row>
-    <row r="818">
+    <row r="818" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C818" s="6"/>
       <c r="F818" s="6"/>
       <c r="I818" s="6"/>
       <c r="K818" s="6"/>
     </row>
-    <row r="819">
+    <row r="819" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C819" s="6"/>
       <c r="F819" s="6"/>
       <c r="I819" s="6"/>
       <c r="K819" s="6"/>
     </row>
-    <row r="820">
+    <row r="820" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C820" s="6"/>
       <c r="F820" s="6"/>
       <c r="I820" s="6"/>
       <c r="K820" s="6"/>
     </row>
-    <row r="821">
+    <row r="821" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C821" s="6"/>
       <c r="F821" s="6"/>
       <c r="I821" s="6"/>
       <c r="K821" s="6"/>
     </row>
-    <row r="822">
+    <row r="822" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C822" s="6"/>
       <c r="F822" s="6"/>
       <c r="I822" s="6"/>
       <c r="K822" s="6"/>
     </row>
-    <row r="823">
+    <row r="823" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C823" s="6"/>
       <c r="F823" s="6"/>
       <c r="I823" s="6"/>
       <c r="K823" s="6"/>
     </row>
-    <row r="824">
+    <row r="824" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C824" s="6"/>
       <c r="F824" s="6"/>
       <c r="I824" s="6"/>
       <c r="K824" s="6"/>
     </row>
-    <row r="825">
+    <row r="825" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C825" s="6"/>
       <c r="F825" s="6"/>
       <c r="I825" s="6"/>
       <c r="K825" s="6"/>
     </row>
-    <row r="826">
+    <row r="826" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C826" s="6"/>
       <c r="F826" s="6"/>
       <c r="I826" s="6"/>
       <c r="K826" s="6"/>
     </row>
-    <row r="827">
+    <row r="827" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C827" s="6"/>
       <c r="F827" s="6"/>
       <c r="I827" s="6"/>
       <c r="K827" s="6"/>
     </row>
-    <row r="828">
+    <row r="828" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C828" s="6"/>
       <c r="F828" s="6"/>
       <c r="I828" s="6"/>
       <c r="K828" s="6"/>
     </row>
-    <row r="829">
+    <row r="829" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C829" s="6"/>
       <c r="F829" s="6"/>
       <c r="I829" s="6"/>
       <c r="K829" s="6"/>
     </row>
-    <row r="830">
+    <row r="830" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C830" s="6"/>
       <c r="F830" s="6"/>
       <c r="I830" s="6"/>
       <c r="K830" s="6"/>
     </row>
-    <row r="831">
+    <row r="831" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C831" s="6"/>
       <c r="F831" s="6"/>
       <c r="I831" s="6"/>
       <c r="K831" s="6"/>
     </row>
-    <row r="832">
+    <row r="832" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C832" s="6"/>
       <c r="F832" s="6"/>
       <c r="I832" s="6"/>
       <c r="K832" s="6"/>
     </row>
-    <row r="833">
+    <row r="833" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C833" s="6"/>
       <c r="F833" s="6"/>
       <c r="I833" s="6"/>
       <c r="K833" s="6"/>
     </row>
-    <row r="834">
+    <row r="834" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C834" s="6"/>
       <c r="F834" s="6"/>
       <c r="I834" s="6"/>
       <c r="K834" s="6"/>
     </row>
-    <row r="835">
+    <row r="835" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C835" s="6"/>
       <c r="F835" s="6"/>
       <c r="I835" s="6"/>
       <c r="K835" s="6"/>
     </row>
-    <row r="836">
+    <row r="836" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C836" s="6"/>
       <c r="F836" s="6"/>
       <c r="I836" s="6"/>
       <c r="K836" s="6"/>
     </row>
-    <row r="837">
+    <row r="837" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C837" s="6"/>
       <c r="F837" s="6"/>
       <c r="I837" s="6"/>
       <c r="K837" s="6"/>
     </row>
-    <row r="838">
+    <row r="838" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C838" s="6"/>
       <c r="F838" s="6"/>
       <c r="I838" s="6"/>
       <c r="K838" s="6"/>
     </row>
-    <row r="839">
+    <row r="839" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C839" s="6"/>
       <c r="F839" s="6"/>
       <c r="I839" s="6"/>
       <c r="K839" s="6"/>
     </row>
-    <row r="840">
+    <row r="840" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C840" s="6"/>
       <c r="F840" s="6"/>
       <c r="I840" s="6"/>
       <c r="K840" s="6"/>
     </row>
-    <row r="841">
+    <row r="841" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C841" s="6"/>
       <c r="F841" s="6"/>
       <c r="I841" s="6"/>
       <c r="K841" s="6"/>
     </row>
-    <row r="842">
+    <row r="842" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C842" s="6"/>
       <c r="F842" s="6"/>
       <c r="I842" s="6"/>
       <c r="K842" s="6"/>
     </row>
-    <row r="843">
+    <row r="843" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C843" s="6"/>
       <c r="F843" s="6"/>
       <c r="I843" s="6"/>
       <c r="K843" s="6"/>
     </row>
-    <row r="844">
+    <row r="844" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C844" s="6"/>
       <c r="F844" s="6"/>
       <c r="I844" s="6"/>
       <c r="K844" s="6"/>
     </row>
-    <row r="845">
+    <row r="845" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C845" s="6"/>
       <c r="F845" s="6"/>
       <c r="I845" s="6"/>
       <c r="K845" s="6"/>
     </row>
-    <row r="846">
+    <row r="846" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C846" s="6"/>
       <c r="F846" s="6"/>
       <c r="I846" s="6"/>
       <c r="K846" s="6"/>
     </row>
-    <row r="847">
+    <row r="847" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C847" s="6"/>
       <c r="F847" s="6"/>
       <c r="I847" s="6"/>
       <c r="K847" s="6"/>
     </row>
-    <row r="848">
+    <row r="848" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C848" s="6"/>
       <c r="F848" s="6"/>
       <c r="I848" s="6"/>
       <c r="K848" s="6"/>
     </row>
-    <row r="849">
+    <row r="849" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C849" s="6"/>
       <c r="F849" s="6"/>
       <c r="I849" s="6"/>
       <c r="K849" s="6"/>
     </row>
-    <row r="850">
+    <row r="850" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C850" s="6"/>
       <c r="F850" s="6"/>
       <c r="I850" s="6"/>
       <c r="K850" s="6"/>
     </row>
-    <row r="851">
+    <row r="851" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C851" s="6"/>
       <c r="F851" s="6"/>
       <c r="I851" s="6"/>
       <c r="K851" s="6"/>
     </row>
-    <row r="852">
+    <row r="852" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C852" s="6"/>
       <c r="F852" s="6"/>
       <c r="I852" s="6"/>
       <c r="K852" s="6"/>
     </row>
-    <row r="853">
+    <row r="853" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C853" s="6"/>
       <c r="F853" s="6"/>
       <c r="I853" s="6"/>
       <c r="K853" s="6"/>
     </row>
-    <row r="854">
+    <row r="854" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C854" s="6"/>
       <c r="F854" s="6"/>
       <c r="I854" s="6"/>
       <c r="K854" s="6"/>
     </row>
-    <row r="855">
+    <row r="855" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C855" s="6"/>
       <c r="F855" s="6"/>
       <c r="I855" s="6"/>
       <c r="K855" s="6"/>
     </row>
-    <row r="856">
+    <row r="856" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C856" s="6"/>
       <c r="F856" s="6"/>
       <c r="I856" s="6"/>
       <c r="K856" s="6"/>
     </row>
-    <row r="857">
+    <row r="857" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C857" s="6"/>
       <c r="F857" s="6"/>
       <c r="I857" s="6"/>
       <c r="K857" s="6"/>
     </row>
-    <row r="858">
+    <row r="858" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C858" s="6"/>
       <c r="F858" s="6"/>
       <c r="I858" s="6"/>
       <c r="K858" s="6"/>
     </row>
-    <row r="859">
+    <row r="859" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C859" s="6"/>
       <c r="F859" s="6"/>
       <c r="I859" s="6"/>
       <c r="K859" s="6"/>
     </row>
-    <row r="860">
+    <row r="860" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C860" s="6"/>
       <c r="F860" s="6"/>
       <c r="I860" s="6"/>
       <c r="K860" s="6"/>
     </row>
-    <row r="861">
+    <row r="861" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C861" s="6"/>
       <c r="F861" s="6"/>
       <c r="I861" s="6"/>
       <c r="K861" s="6"/>
     </row>
-    <row r="862">
+    <row r="862" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C862" s="6"/>
       <c r="F862" s="6"/>
       <c r="I862" s="6"/>
       <c r="K862" s="6"/>
     </row>
-    <row r="863">
+    <row r="863" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C863" s="6"/>
       <c r="F863" s="6"/>
       <c r="I863" s="6"/>
       <c r="K863" s="6"/>
     </row>
-    <row r="864">
+    <row r="864" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C864" s="6"/>
       <c r="F864" s="6"/>
       <c r="I864" s="6"/>
       <c r="K864" s="6"/>
     </row>
-    <row r="865">
+    <row r="865" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C865" s="6"/>
       <c r="F865" s="6"/>
       <c r="I865" s="6"/>
       <c r="K865" s="6"/>
     </row>
-    <row r="866">
+    <row r="866" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C866" s="6"/>
       <c r="F866" s="6"/>
       <c r="I866" s="6"/>
       <c r="K866" s="6"/>
     </row>
-    <row r="867">
+    <row r="867" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C867" s="6"/>
       <c r="F867" s="6"/>
       <c r="I867" s="6"/>
       <c r="K867" s="6"/>
     </row>
-    <row r="868">
+    <row r="868" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C868" s="6"/>
       <c r="F868" s="6"/>
       <c r="I868" s="6"/>
       <c r="K868" s="6"/>
     </row>
-    <row r="869">
+    <row r="869" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C869" s="6"/>
       <c r="F869" s="6"/>
       <c r="I869" s="6"/>
       <c r="K869" s="6"/>
     </row>
-    <row r="870">
+    <row r="870" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C870" s="6"/>
       <c r="F870" s="6"/>
       <c r="I870" s="6"/>
       <c r="K870" s="6"/>
     </row>
-    <row r="871">
+    <row r="871" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C871" s="6"/>
       <c r="F871" s="6"/>
       <c r="I871" s="6"/>
       <c r="K871" s="6"/>
     </row>
-    <row r="872">
+    <row r="872" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C872" s="6"/>
       <c r="F872" s="6"/>
       <c r="I872" s="6"/>
       <c r="K872" s="6"/>
     </row>
-    <row r="873">
+    <row r="873" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C873" s="6"/>
       <c r="F873" s="6"/>
       <c r="I873" s="6"/>
       <c r="K873" s="6"/>
     </row>
-    <row r="874">
+    <row r="874" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C874" s="6"/>
       <c r="F874" s="6"/>
       <c r="I874" s="6"/>
       <c r="K874" s="6"/>
     </row>
-    <row r="875">
+    <row r="875" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C875" s="6"/>
       <c r="F875" s="6"/>
       <c r="I875" s="6"/>
       <c r="K875" s="6"/>
     </row>
-    <row r="876">
+    <row r="876" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C876" s="6"/>
       <c r="F876" s="6"/>
       <c r="I876" s="6"/>
       <c r="K876" s="6"/>
     </row>
-    <row r="877">
+    <row r="877" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C877" s="6"/>
       <c r="F877" s="6"/>
       <c r="I877" s="6"/>
       <c r="K877" s="6"/>
     </row>
-    <row r="878">
+    <row r="878" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C878" s="6"/>
       <c r="F878" s="6"/>
       <c r="I878" s="6"/>
       <c r="K878" s="6"/>
     </row>
-    <row r="879">
+    <row r="879" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C879" s="6"/>
       <c r="F879" s="6"/>
       <c r="I879" s="6"/>
       <c r="K879" s="6"/>
     </row>
-    <row r="880">
+    <row r="880" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C880" s="6"/>
       <c r="F880" s="6"/>
       <c r="I880" s="6"/>
       <c r="K880" s="6"/>
     </row>
-    <row r="881">
+    <row r="881" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C881" s="6"/>
       <c r="F881" s="6"/>
       <c r="I881" s="6"/>
       <c r="K881" s="6"/>
     </row>
-    <row r="882">
+    <row r="882" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C882" s="6"/>
       <c r="F882" s="6"/>
       <c r="I882" s="6"/>
       <c r="K882" s="6"/>
     </row>
-    <row r="883">
+    <row r="883" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C883" s="6"/>
       <c r="F883" s="6"/>
       <c r="I883" s="6"/>
       <c r="K883" s="6"/>
     </row>
-    <row r="884">
+    <row r="884" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C884" s="6"/>
       <c r="F884" s="6"/>
       <c r="I884" s="6"/>
       <c r="K884" s="6"/>
     </row>
-    <row r="885">
+    <row r="885" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C885" s="6"/>
       <c r="F885" s="6"/>
       <c r="I885" s="6"/>
       <c r="K885" s="6"/>
     </row>
-    <row r="886">
+    <row r="886" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C886" s="6"/>
       <c r="F886" s="6"/>
       <c r="I886" s="6"/>
       <c r="K886" s="6"/>
     </row>
-    <row r="887">
+    <row r="887" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C887" s="6"/>
       <c r="F887" s="6"/>
       <c r="I887" s="6"/>
       <c r="K887" s="6"/>
     </row>
-    <row r="888">
+    <row r="888" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C888" s="6"/>
       <c r="F888" s="6"/>
       <c r="I888" s="6"/>
       <c r="K888" s="6"/>
     </row>
-    <row r="889">
+    <row r="889" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C889" s="6"/>
       <c r="F889" s="6"/>
       <c r="I889" s="6"/>
       <c r="K889" s="6"/>
     </row>
-    <row r="890">
+    <row r="890" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C890" s="6"/>
       <c r="F890" s="6"/>
       <c r="I890" s="6"/>
       <c r="K890" s="6"/>
     </row>
-    <row r="891">
+    <row r="891" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C891" s="6"/>
       <c r="F891" s="6"/>
       <c r="I891" s="6"/>
       <c r="K891" s="6"/>
     </row>
-    <row r="892">
+    <row r="892" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C892" s="6"/>
       <c r="F892" s="6"/>
       <c r="I892" s="6"/>
       <c r="K892" s="6"/>
     </row>
-    <row r="893">
+    <row r="893" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C893" s="6"/>
       <c r="F893" s="6"/>
       <c r="I893" s="6"/>
       <c r="K893" s="6"/>
     </row>
-    <row r="894">
+    <row r="894" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C894" s="6"/>
       <c r="F894" s="6"/>
       <c r="I894" s="6"/>
       <c r="K894" s="6"/>
     </row>
-    <row r="895">
+    <row r="895" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C895" s="6"/>
       <c r="F895" s="6"/>
       <c r="I895" s="6"/>
       <c r="K895" s="6"/>
     </row>
-    <row r="896">
+    <row r="896" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C896" s="6"/>
       <c r="F896" s="6"/>
       <c r="I896" s="6"/>
       <c r="K896" s="6"/>
     </row>
-    <row r="897">
+    <row r="897" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C897" s="6"/>
       <c r="F897" s="6"/>
       <c r="I897" s="6"/>
       <c r="K897" s="6"/>
     </row>
-    <row r="898">
+    <row r="898" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C898" s="6"/>
       <c r="F898" s="6"/>
       <c r="I898" s="6"/>
       <c r="K898" s="6"/>
     </row>
-    <row r="899">
+    <row r="899" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C899" s="6"/>
       <c r="F899" s="6"/>
       <c r="I899" s="6"/>
       <c r="K899" s="6"/>
     </row>
-    <row r="900">
+    <row r="900" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C900" s="6"/>
       <c r="F900" s="6"/>
       <c r="I900" s="6"/>
       <c r="K900" s="6"/>
     </row>
-    <row r="901">
+    <row r="901" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C901" s="6"/>
       <c r="F901" s="6"/>
       <c r="I901" s="6"/>
       <c r="K901" s="6"/>
     </row>
-    <row r="902">
+    <row r="902" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C902" s="6"/>
       <c r="F902" s="6"/>
       <c r="I902" s="6"/>
       <c r="K902" s="6"/>
     </row>
-    <row r="903">
+    <row r="903" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C903" s="6"/>
       <c r="F903" s="6"/>
       <c r="I903" s="6"/>
       <c r="K903" s="6"/>
     </row>
-    <row r="904">
+    <row r="904" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C904" s="6"/>
       <c r="F904" s="6"/>
       <c r="I904" s="6"/>
       <c r="K904" s="6"/>
     </row>
-    <row r="905">
+    <row r="905" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C905" s="6"/>
       <c r="F905" s="6"/>
       <c r="I905" s="6"/>
       <c r="K905" s="6"/>
     </row>
-    <row r="906">
+    <row r="906" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C906" s="6"/>
       <c r="F906" s="6"/>
       <c r="I906" s="6"/>
       <c r="K906" s="6"/>
     </row>
-    <row r="907">
+    <row r="907" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C907" s="6"/>
       <c r="F907" s="6"/>
       <c r="I907" s="6"/>
       <c r="K907" s="6"/>
     </row>
-    <row r="908">
+    <row r="908" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C908" s="6"/>
       <c r="F908" s="6"/>
       <c r="I908" s="6"/>
       <c r="K908" s="6"/>
     </row>
-    <row r="909">
+    <row r="909" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C909" s="6"/>
       <c r="F909" s="6"/>
       <c r="I909" s="6"/>
       <c r="K909" s="6"/>
     </row>
-    <row r="910">
+    <row r="910" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C910" s="6"/>
       <c r="F910" s="6"/>
       <c r="I910" s="6"/>
       <c r="K910" s="6"/>
     </row>
-    <row r="911">
+    <row r="911" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C911" s="6"/>
       <c r="F911" s="6"/>
       <c r="I911" s="6"/>
       <c r="K911" s="6"/>
     </row>
-    <row r="912">
+    <row r="912" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C912" s="6"/>
       <c r="F912" s="6"/>
       <c r="I912" s="6"/>
       <c r="K912" s="6"/>
     </row>
-    <row r="913">
+    <row r="913" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C913" s="6"/>
       <c r="F913" s="6"/>
       <c r="I913" s="6"/>
       <c r="K913" s="6"/>
     </row>
-    <row r="914">
+    <row r="914" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C914" s="6"/>
       <c r="F914" s="6"/>
       <c r="I914" s="6"/>
       <c r="K914" s="6"/>
     </row>
-    <row r="915">
+    <row r="915" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C915" s="6"/>
       <c r="F915" s="6"/>
       <c r="I915" s="6"/>
       <c r="K915" s="6"/>
     </row>
-    <row r="916">
+    <row r="916" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C916" s="6"/>
       <c r="F916" s="6"/>
       <c r="I916" s="6"/>
       <c r="K916" s="6"/>
     </row>
-    <row r="917">
+    <row r="917" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C917" s="6"/>
       <c r="F917" s="6"/>
       <c r="I917" s="6"/>
       <c r="K917" s="6"/>
     </row>
-    <row r="918">
+    <row r="918" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C918" s="6"/>
       <c r="F918" s="6"/>
       <c r="I918" s="6"/>
       <c r="K918" s="6"/>
     </row>
-    <row r="919">
+    <row r="919" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C919" s="6"/>
       <c r="F919" s="6"/>
       <c r="I919" s="6"/>
       <c r="K919" s="6"/>
     </row>
-    <row r="920">
+    <row r="920" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C920" s="6"/>
       <c r="F920" s="6"/>
       <c r="I920" s="6"/>
       <c r="K920" s="6"/>
     </row>
-    <row r="921">
+    <row r="921" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C921" s="6"/>
       <c r="F921" s="6"/>
       <c r="I921" s="6"/>
       <c r="K921" s="6"/>
     </row>
-    <row r="922">
+    <row r="922" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C922" s="6"/>
       <c r="F922" s="6"/>
       <c r="I922" s="6"/>
       <c r="K922" s="6"/>
     </row>
-    <row r="923">
+    <row r="923" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C923" s="6"/>
       <c r="F923" s="6"/>
       <c r="I923" s="6"/>
       <c r="K923" s="6"/>
     </row>
-    <row r="924">
+    <row r="924" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C924" s="6"/>
       <c r="F924" s="6"/>
       <c r="I924" s="6"/>
       <c r="K924" s="6"/>
     </row>
-    <row r="925">
+    <row r="925" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C925" s="6"/>
       <c r="F925" s="6"/>
       <c r="I925" s="6"/>
       <c r="K925" s="6"/>
     </row>
-    <row r="926">
+    <row r="926" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C926" s="6"/>
       <c r="F926" s="6"/>
       <c r="I926" s="6"/>
       <c r="K926" s="6"/>
     </row>
-    <row r="927">
+    <row r="927" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C927" s="6"/>
       <c r="F927" s="6"/>
       <c r="I927" s="6"/>
       <c r="K927" s="6"/>
     </row>
-    <row r="928">
+    <row r="928" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C928" s="6"/>
       <c r="F928" s="6"/>
       <c r="I928" s="6"/>
       <c r="K928" s="6"/>
     </row>
-    <row r="929">
+    <row r="929" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C929" s="6"/>
       <c r="F929" s="6"/>
       <c r="I929" s="6"/>
       <c r="K929" s="6"/>
     </row>
-    <row r="930">
+    <row r="930" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C930" s="6"/>
       <c r="F930" s="6"/>
       <c r="I930" s="6"/>
       <c r="K930" s="6"/>
     </row>
-    <row r="931">
+    <row r="931" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C931" s="6"/>
       <c r="F931" s="6"/>
       <c r="I931" s="6"/>
       <c r="K931" s="6"/>
     </row>
-    <row r="932">
+    <row r="932" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C932" s="6"/>
       <c r="F932" s="6"/>
       <c r="I932" s="6"/>
       <c r="K932" s="6"/>
     </row>
-    <row r="933">
+    <row r="933" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C933" s="6"/>
       <c r="F933" s="6"/>
       <c r="I933" s="6"/>
       <c r="K933" s="6"/>
     </row>
-    <row r="934">
+    <row r="934" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C934" s="6"/>
       <c r="F934" s="6"/>
       <c r="I934" s="6"/>
       <c r="K934" s="6"/>
     </row>
-    <row r="935">
+    <row r="935" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C935" s="6"/>
       <c r="F935" s="6"/>
       <c r="I935" s="6"/>
       <c r="K935" s="6"/>
     </row>
-    <row r="936">
+    <row r="936" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C936" s="6"/>
       <c r="F936" s="6"/>
       <c r="I936" s="6"/>
       <c r="K936" s="6"/>
     </row>
-    <row r="937">
+    <row r="937" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C937" s="6"/>
       <c r="F937" s="6"/>
       <c r="I937" s="6"/>
       <c r="K937" s="6"/>
     </row>
-    <row r="938">
+    <row r="938" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C938" s="6"/>
       <c r="F938" s="6"/>
       <c r="I938" s="6"/>
       <c r="K938" s="6"/>
     </row>
-    <row r="939">
+    <row r="939" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C939" s="6"/>
       <c r="F939" s="6"/>
       <c r="I939" s="6"/>
       <c r="K939" s="6"/>
     </row>
-    <row r="940">
+    <row r="940" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C940" s="6"/>
       <c r="F940" s="6"/>
       <c r="I940" s="6"/>
       <c r="K940" s="6"/>
     </row>
-    <row r="941">
+    <row r="941" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C941" s="6"/>
       <c r="F941" s="6"/>
       <c r="I941" s="6"/>
       <c r="K941" s="6"/>
     </row>
-    <row r="942">
+    <row r="942" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C942" s="6"/>
       <c r="F942" s="6"/>
       <c r="I942" s="6"/>
       <c r="K942" s="6"/>
     </row>
-    <row r="943">
+    <row r="943" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C943" s="6"/>
       <c r="F943" s="6"/>
       <c r="I943" s="6"/>
       <c r="K943" s="6"/>
     </row>
-    <row r="944">
+    <row r="944" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C944" s="6"/>
       <c r="F944" s="6"/>
       <c r="I944" s="6"/>
       <c r="K944" s="6"/>
     </row>
-    <row r="945">
+    <row r="945" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C945" s="6"/>
       <c r="F945" s="6"/>
       <c r="I945" s="6"/>
       <c r="K945" s="6"/>
     </row>
-    <row r="946">
+    <row r="946" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C946" s="6"/>
       <c r="F946" s="6"/>
       <c r="I946" s="6"/>
       <c r="K946" s="6"/>
     </row>
-    <row r="947">
+    <row r="947" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C947" s="6"/>
       <c r="F947" s="6"/>
       <c r="I947" s="6"/>
       <c r="K947" s="6"/>
     </row>
-    <row r="948">
+    <row r="948" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C948" s="6"/>
       <c r="F948" s="6"/>
       <c r="I948" s="6"/>
       <c r="K948" s="6"/>
     </row>
-    <row r="949">
+    <row r="949" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C949" s="6"/>
       <c r="F949" s="6"/>
       <c r="I949" s="6"/>
       <c r="K949" s="6"/>
     </row>
-    <row r="950">
+    <row r="950" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C950" s="6"/>
       <c r="F950" s="6"/>
       <c r="I950" s="6"/>
       <c r="K950" s="6"/>
     </row>
-    <row r="951">
+    <row r="951" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C951" s="6"/>
       <c r="F951" s="6"/>
       <c r="I951" s="6"/>
       <c r="K951" s="6"/>
     </row>
-    <row r="952">
+    <row r="952" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C952" s="6"/>
       <c r="F952" s="6"/>
       <c r="I952" s="6"/>
       <c r="K952" s="6"/>
     </row>
-    <row r="953">
+    <row r="953" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C953" s="6"/>
       <c r="F953" s="6"/>
       <c r="I953" s="6"/>
       <c r="K953" s="6"/>
     </row>
-    <row r="954">
+    <row r="954" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C954" s="6"/>
       <c r="F954" s="6"/>
       <c r="I954" s="6"/>
       <c r="K954" s="6"/>
     </row>
-    <row r="955">
+    <row r="955" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C955" s="6"/>
       <c r="F955" s="6"/>
       <c r="I955" s="6"/>
       <c r="K955" s="6"/>
     </row>
-    <row r="956">
+    <row r="956" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C956" s="6"/>
       <c r="F956" s="6"/>
       <c r="I956" s="6"/>
       <c r="K956" s="6"/>
     </row>
-    <row r="957">
+    <row r="957" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C957" s="6"/>
       <c r="F957" s="6"/>
       <c r="I957" s="6"/>
       <c r="K957" s="6"/>
     </row>
-    <row r="958">
+    <row r="958" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C958" s="6"/>
       <c r="F958" s="6"/>
       <c r="I958" s="6"/>
       <c r="K958" s="6"/>
     </row>
-    <row r="959">
+    <row r="959" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C959" s="6"/>
       <c r="F959" s="6"/>
       <c r="I959" s="6"/>
       <c r="K959" s="6"/>
     </row>
-    <row r="960">
+    <row r="960" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C960" s="6"/>
       <c r="F960" s="6"/>
       <c r="I960" s="6"/>
       <c r="K960" s="6"/>
     </row>
-    <row r="961">
+    <row r="961" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C961" s="6"/>
       <c r="F961" s="6"/>
       <c r="I961" s="6"/>
       <c r="K961" s="6"/>
     </row>
-    <row r="962">
+    <row r="962" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C962" s="6"/>
       <c r="F962" s="6"/>
       <c r="I962" s="6"/>
       <c r="K962" s="6"/>
     </row>
-    <row r="963">
+    <row r="963" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C963" s="6"/>
       <c r="F963" s="6"/>
       <c r="I963" s="6"/>
       <c r="K963" s="6"/>
     </row>
-    <row r="964">
+    <row r="964" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C964" s="6"/>
       <c r="F964" s="6"/>
       <c r="I964" s="6"/>
       <c r="K964" s="6"/>
     </row>
-    <row r="965">
+    <row r="965" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C965" s="6"/>
       <c r="F965" s="6"/>
       <c r="I965" s="6"/>
       <c r="K965" s="6"/>
     </row>
-    <row r="966">
+    <row r="966" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C966" s="6"/>
       <c r="F966" s="6"/>
       <c r="I966" s="6"/>
       <c r="K966" s="6"/>
     </row>
-    <row r="967">
+    <row r="967" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C967" s="6"/>
       <c r="F967" s="6"/>
       <c r="I967" s="6"/>
       <c r="K967" s="6"/>
     </row>
-    <row r="968">
+    <row r="968" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C968" s="6"/>
       <c r="F968" s="6"/>
       <c r="I968" s="6"/>
       <c r="K968" s="6"/>
     </row>
-    <row r="969">
+    <row r="969" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C969" s="6"/>
       <c r="F969" s="6"/>
       <c r="I969" s="6"/>
       <c r="K969" s="6"/>
     </row>
-    <row r="970">
+    <row r="970" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C970" s="6"/>
       <c r="F970" s="6"/>
       <c r="I970" s="6"/>
       <c r="K970" s="6"/>
     </row>
-    <row r="971">
+    <row r="971" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C971" s="6"/>
       <c r="F971" s="6"/>
       <c r="I971" s="6"/>
       <c r="K971" s="6"/>
     </row>
-    <row r="972">
+    <row r="972" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C972" s="6"/>
       <c r="F972" s="6"/>
       <c r="I972" s="6"/>
       <c r="K972" s="6"/>
     </row>
-    <row r="973">
+    <row r="973" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C973" s="6"/>
       <c r="F973" s="6"/>
       <c r="I973" s="6"/>
       <c r="K973" s="6"/>
     </row>
-    <row r="974">
+    <row r="974" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C974" s="6"/>
       <c r="F974" s="6"/>
       <c r="I974" s="6"/>
       <c r="K974" s="6"/>
     </row>
-    <row r="975">
+    <row r="975" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C975" s="6"/>
       <c r="F975" s="6"/>
       <c r="I975" s="6"/>
       <c r="K975" s="6"/>
     </row>
-    <row r="976">
+    <row r="976" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C976" s="6"/>
       <c r="F976" s="6"/>
       <c r="I976" s="6"/>
       <c r="K976" s="6"/>
     </row>
-    <row r="977">
+    <row r="977" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C977" s="6"/>
       <c r="F977" s="6"/>
       <c r="I977" s="6"/>
       <c r="K977" s="6"/>
     </row>
-    <row r="978">
+    <row r="978" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C978" s="6"/>
       <c r="F978" s="6"/>
       <c r="I978" s="6"/>
       <c r="K978" s="6"/>
     </row>
-    <row r="979">
+    <row r="979" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C979" s="6"/>
       <c r="F979" s="6"/>
       <c r="I979" s="6"/>
       <c r="K979" s="6"/>
     </row>
-    <row r="980">
+    <row r="980" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C980" s="6"/>
       <c r="F980" s="6"/>
       <c r="I980" s="6"/>
       <c r="K980" s="6"/>
     </row>
-    <row r="981">
+    <row r="981" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C981" s="6"/>
       <c r="F981" s="6"/>
       <c r="I981" s="6"/>
       <c r="K981" s="6"/>
     </row>
-    <row r="982">
+    <row r="982" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C982" s="6"/>
       <c r="F982" s="6"/>
       <c r="I982" s="6"/>
       <c r="K982" s="6"/>
     </row>
-    <row r="983">
+    <row r="983" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C983" s="6"/>
       <c r="F983" s="6"/>
       <c r="I983" s="6"/>
       <c r="K983" s="6"/>
     </row>
-    <row r="984">
+    <row r="984" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C984" s="6"/>
       <c r="F984" s="6"/>
       <c r="I984" s="6"/>
       <c r="K984" s="6"/>
     </row>
-    <row r="985">
+    <row r="985" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C985" s="6"/>
       <c r="F985" s="6"/>
       <c r="I985" s="6"/>
       <c r="K985" s="6"/>
     </row>
-    <row r="986">
+    <row r="986" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C986" s="6"/>
       <c r="F986" s="6"/>
       <c r="I986" s="6"/>
       <c r="K986" s="6"/>
     </row>
-    <row r="987">
+    <row r="987" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C987" s="6"/>
       <c r="F987" s="6"/>
       <c r="I987" s="6"/>
       <c r="K987" s="6"/>
     </row>
-    <row r="988">
+    <row r="988" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C988" s="6"/>
       <c r="F988" s="6"/>
       <c r="I988" s="6"/>
       <c r="K988" s="6"/>
     </row>
-    <row r="989">
+    <row r="989" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C989" s="6"/>
       <c r="F989" s="6"/>
       <c r="I989" s="6"/>
       <c r="K989" s="6"/>
     </row>
-    <row r="990">
+    <row r="990" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C990" s="6"/>
       <c r="F990" s="6"/>
       <c r="I990" s="6"/>
       <c r="K990" s="6"/>
     </row>
-    <row r="991">
+    <row r="991" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C991" s="6"/>
       <c r="F991" s="6"/>
       <c r="I991" s="6"/>
       <c r="K991" s="6"/>
     </row>
-    <row r="992">
+    <row r="992" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C992" s="6"/>
       <c r="F992" s="6"/>
       <c r="I992" s="6"/>
       <c r="K992" s="6"/>
     </row>
-    <row r="993">
+    <row r="993" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C993" s="6"/>
       <c r="F993" s="6"/>
       <c r="I993" s="6"/>
       <c r="K993" s="6"/>
     </row>
-    <row r="994">
+    <row r="994" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C994" s="6"/>
       <c r="F994" s="6"/>
       <c r="I994" s="6"/>
       <c r="K994" s="6"/>
     </row>
-    <row r="995">
+    <row r="995" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C995" s="6"/>
       <c r="F995" s="6"/>
       <c r="I995" s="6"/>
       <c r="K995" s="6"/>
     </row>
-    <row r="996">
+    <row r="996" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C996" s="6"/>
       <c r="F996" s="6"/>
       <c r="I996" s="6"/>
       <c r="K996" s="6"/>
     </row>
-    <row r="997">
+    <row r="997" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C997" s="6"/>
       <c r="F997" s="6"/>
       <c r="I997" s="6"/>
       <c r="K997" s="6"/>
     </row>
-    <row r="998">
+    <row r="998" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C998" s="6"/>
       <c r="F998" s="6"/>
       <c r="I998" s="6"/>
       <c r="K998" s="6"/>
     </row>
-    <row r="999">
+    <row r="999" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C999" s="6"/>
       <c r="F999" s="6"/>
       <c r="I999" s="6"/>
       <c r="K999" s="6"/>
     </row>
-    <row r="1000">
+    <row r="1000" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C1000" s="6"/>
       <c r="F1000" s="6"/>
       <c r="I1000" s="6"/>
       <c r="K1000" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$L$66"/>
-  <drawing r:id="rId1"/>
+  <autoFilter ref="A1:L66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos/Equivalencias_LLYA.xlsx
+++ b/datos/Equivalencias_LLYA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consumo_horas_educacion_secundaria\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5B6277-125C-4260-A888-30B669BFB6BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819C922B-92B2-4AF5-9CD3-E0BB6A4ECFB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1381,10 +1381,10 @@
         <v>15</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I25" s="5">
         <v>5</v>
